--- a/GameConfig/Datas/模型/模型配置表.xlsx
+++ b/GameConfig/Datas/模型/模型配置表.xlsx
@@ -1,19 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="29127"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet">
+  <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Unity\GitHub Project\DGame_Fantasy\GameConfig\Datas\通用配置表\"/>
-    </mc:Choice>
-  </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F6644890-9624-47CD-9CED-CE6CEAB6A196}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="57480" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView windowHeight="17655"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
+    <sheet name="角色模型配置表" sheetId="1" r:id="rId1"/>
+    <sheet name="怪物模型配置表" sheetId="2" r:id="rId2"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -33,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="51" uniqueCount="40">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="200" uniqueCount="70">
   <si>
     <t>##var</t>
   </si>
@@ -86,6 +81,48 @@
     <t>ShadowOffsetY</t>
   </si>
   <si>
+    <t>BaseMoveSpeed</t>
+  </si>
+  <si>
+    <t>EnableCollision</t>
+  </si>
+  <si>
+    <t>UseAabbCollision</t>
+  </si>
+  <si>
+    <t>CollisionRadius</t>
+  </si>
+  <si>
+    <t>CollisionHeight</t>
+  </si>
+  <si>
+    <t>HpBarOffsetX</t>
+  </si>
+  <si>
+    <t>HpBarOffsetY</t>
+  </si>
+  <si>
+    <t>HitFlashColorR</t>
+  </si>
+  <si>
+    <t>HitFlashColorG</t>
+  </si>
+  <si>
+    <t>HitFlashColorB</t>
+  </si>
+  <si>
+    <t>HitFullFlashTime</t>
+  </si>
+  <si>
+    <t>HitFlashTime</t>
+  </si>
+  <si>
+    <t>DeathFadeOutDurTime</t>
+  </si>
+  <si>
+    <t>DeathEffectSoundID</t>
+  </si>
+  <si>
     <t>##type</t>
   </si>
   <si>
@@ -101,9 +138,15 @@
     <t>byte</t>
   </si>
   <si>
+    <t>bool</t>
+  </si>
+  <si>
     <t>##group</t>
   </si>
   <si>
+    <t/>
+  </si>
+  <si>
     <t>##</t>
   </si>
   <si>
@@ -153,13 +196,61 @@
   </si>
   <si>
     <t>阴影偏移Y</t>
+  </si>
+  <si>
+    <t>参考移动速度</t>
+  </si>
+  <si>
+    <t>是否开启碰撞</t>
+  </si>
+  <si>
+    <t>是否矩形碰撞</t>
+  </si>
+  <si>
+    <t>碰撞半径</t>
+  </si>
+  <si>
+    <t>碰撞高度</t>
+  </si>
+  <si>
+    <t>血条高度偏移X</t>
+  </si>
+  <si>
+    <t>血条高度偏移Y</t>
+  </si>
+  <si>
+    <t>受击高亮R</t>
+  </si>
+  <si>
+    <t>受击高亮G</t>
+  </si>
+  <si>
+    <t>受击高亮B</t>
+  </si>
+  <si>
+    <t>受击高亮总持续时间</t>
+  </si>
+  <si>
+    <t>受击高亮持续时间</t>
+  </si>
+  <si>
+    <t>死亡渐变消失时间</t>
+  </si>
+  <si>
+    <t>死亡音效ID</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="4" x14ac:knownFonts="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="xr9">
+  <numFmts count="4">
+    <numFmt numFmtId="41" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
+    <numFmt numFmtId="42" formatCode="_ &quot;￥&quot;* #,##0_ ;_ &quot;￥&quot;* \-#,##0_ ;_ &quot;￥&quot;* &quot;-&quot;_ ;_ @_ "/>
+    <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
+  </numFmts>
+  <fonts count="20">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -171,7 +262,6 @@
       <sz val="11"/>
       <color rgb="FF006100"/>
       <name val="等线"/>
-      <family val="3"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
@@ -179,19 +269,141 @@
       <sz val="11"/>
       <color rgb="FF9C0006"/>
       <name val="等线"/>
-      <family val="3"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="9"/>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF0000FF"/>
       <name val="等线"/>
-      <family val="3"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF800080"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="18"/>
+      <color theme="3"/>
+      <name val="等线"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <i/>
+      <sz val="11"/>
+      <color rgb="FF7F7F7F"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="15"/>
+      <color theme="3"/>
+      <name val="等线"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="13"/>
+      <color theme="3"/>
+      <name val="等线"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="3"/>
+      <name val="等线"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF3F3F76"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF3F3F3F"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C6500"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="0"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
-  <fills count="5">
+  <fills count="34">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -212,12 +424,186 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.59999389629810485"/>
+        <fgColor theme="9" tint="0.6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFCC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFCC99"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2F2F2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA5A5A5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFEB9C"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="10">
     <border>
       <left/>
       <right/>
@@ -240,68 +626,341 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFB2B2B2"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFB2B2B2"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFB2B2B2"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFB2B2B2"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4" tint="0.499984740745262"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF7F7F7F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF7F7F7F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF7F7F7F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF7F7F7F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="double">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="double">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="double">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="double">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="double">
+        <color rgb="FFFF8001"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color theme="4"/>
+      </top>
+      <bottom style="double">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
-  <cellStyleXfs count="3">
+  <cellStyleXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="41" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="2" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="7" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="8" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="8" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="9" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="15">
+  <cellXfs count="14">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="2" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="22" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="23" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="22" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="1" xfId="22" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="23" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="1" xfId="23" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="5" borderId="1" xfId="22" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="2" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="1" xfId="23" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="4" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="1" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="1" xfId="2" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1"/>
   </cellXfs>
-  <cellStyles count="3">
-    <cellStyle name="差" xfId="2" builtinId="27"/>
+  <cellStyles count="49">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
-    <cellStyle name="好" xfId="1" builtinId="26"/>
+    <cellStyle name="千位分隔" xfId="1" builtinId="3"/>
+    <cellStyle name="货币" xfId="2" builtinId="4"/>
+    <cellStyle name="百分比" xfId="3" builtinId="5"/>
+    <cellStyle name="千位分隔[0]" xfId="4" builtinId="6"/>
+    <cellStyle name="货币[0]" xfId="5" builtinId="7"/>
+    <cellStyle name="超链接" xfId="6" builtinId="8"/>
+    <cellStyle name="已访问的超链接" xfId="7" builtinId="9"/>
+    <cellStyle name="注释" xfId="8" builtinId="10"/>
+    <cellStyle name="警告文本" xfId="9" builtinId="11"/>
+    <cellStyle name="标题" xfId="10" builtinId="15"/>
+    <cellStyle name="解释性文本" xfId="11" builtinId="53"/>
+    <cellStyle name="标题 1" xfId="12" builtinId="16"/>
+    <cellStyle name="标题 2" xfId="13" builtinId="17"/>
+    <cellStyle name="标题 3" xfId="14" builtinId="18"/>
+    <cellStyle name="标题 4" xfId="15" builtinId="19"/>
+    <cellStyle name="输入" xfId="16" builtinId="20"/>
+    <cellStyle name="输出" xfId="17" builtinId="21"/>
+    <cellStyle name="计算" xfId="18" builtinId="22"/>
+    <cellStyle name="检查单元格" xfId="19" builtinId="23"/>
+    <cellStyle name="链接单元格" xfId="20" builtinId="24"/>
+    <cellStyle name="汇总" xfId="21" builtinId="25"/>
+    <cellStyle name="好" xfId="22" builtinId="26"/>
+    <cellStyle name="差" xfId="23" builtinId="27"/>
+    <cellStyle name="适中" xfId="24" builtinId="28"/>
+    <cellStyle name="强调文字颜色 1" xfId="25" builtinId="29"/>
+    <cellStyle name="20% - 强调文字颜色 1" xfId="26" builtinId="30"/>
+    <cellStyle name="40% - 强调文字颜色 1" xfId="27" builtinId="31"/>
+    <cellStyle name="60% - 强调文字颜色 1" xfId="28" builtinId="32"/>
+    <cellStyle name="强调文字颜色 2" xfId="29" builtinId="33"/>
+    <cellStyle name="20% - 强调文字颜色 2" xfId="30" builtinId="34"/>
+    <cellStyle name="40% - 强调文字颜色 2" xfId="31" builtinId="35"/>
+    <cellStyle name="60% - 强调文字颜色 2" xfId="32" builtinId="36"/>
+    <cellStyle name="强调文字颜色 3" xfId="33" builtinId="37"/>
+    <cellStyle name="20% - 强调文字颜色 3" xfId="34" builtinId="38"/>
+    <cellStyle name="40% - 强调文字颜色 3" xfId="35" builtinId="39"/>
+    <cellStyle name="60% - 强调文字颜色 3" xfId="36" builtinId="40"/>
+    <cellStyle name="强调文字颜色 4" xfId="37" builtinId="41"/>
+    <cellStyle name="20% - 强调文字颜色 4" xfId="38" builtinId="42"/>
+    <cellStyle name="40% - 强调文字颜色 4" xfId="39" builtinId="43"/>
+    <cellStyle name="60% - 强调文字颜色 4" xfId="40" builtinId="44"/>
+    <cellStyle name="强调文字颜色 5" xfId="41" builtinId="45"/>
+    <cellStyle name="20% - 强调文字颜色 5" xfId="42" builtinId="46"/>
+    <cellStyle name="40% - 强调文字颜色 5" xfId="43" builtinId="47"/>
+    <cellStyle name="60% - 强调文字颜色 5" xfId="44" builtinId="48"/>
+    <cellStyle name="强调文字颜色 6" xfId="45" builtinId="49"/>
+    <cellStyle name="20% - 强调文字颜色 6" xfId="46" builtinId="50"/>
+    <cellStyle name="40% - 强调文字颜色 6" xfId="47" builtinId="51"/>
+    <cellStyle name="60% - 强调文字颜色 6" xfId="48" builtinId="52"/>
   </cellStyles>
-  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
       <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
-    </ext>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
-      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
     </ext>
   </extLst>
 </styleSheet>
@@ -559,40 +1218,51 @@
     </a:fmtScheme>
   </a:themeElements>
   <a:objectDefaults/>
-  <a:extraClrSchemeLst/>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:AJ14"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14" x14ac:dyDescent="0.3"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
+  <dimension ref="A1:AE14"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25"/>
   <cols>
     <col min="1" max="1" width="9.25" customWidth="1"/>
-    <col min="2" max="2" width="17.33203125" customWidth="1"/>
-    <col min="3" max="3" width="12.4140625" style="14" customWidth="1"/>
+    <col min="2" max="2" width="17.3333333333333" customWidth="1"/>
+    <col min="3" max="3" width="12.4166666666667" style="8" customWidth="1"/>
     <col min="4" max="6" width="22.5" customWidth="1"/>
     <col min="7" max="12" width="18.75" customWidth="1"/>
-    <col min="13" max="17" width="18.75" style="3" customWidth="1"/>
+    <col min="13" max="18" width="18.75" style="9" customWidth="1"/>
+    <col min="19" max="19" width="18.9333333333333" customWidth="1"/>
+    <col min="20" max="20" width="22.9833333333333" customWidth="1"/>
+    <col min="21" max="21" width="15.9583333333333" customWidth="1"/>
+    <col min="22" max="22" width="16.725" customWidth="1"/>
+    <col min="23" max="23" width="17.3" customWidth="1"/>
+    <col min="24" max="24" width="18.55" customWidth="1"/>
+    <col min="25" max="26" width="16.3416666666667" customWidth="1"/>
+    <col min="27" max="28" width="20.2833333333333" customWidth="1"/>
+    <col min="29" max="29" width="19.225" customWidth="1"/>
+    <col min="30" max="30" width="22.875" customWidth="1"/>
+    <col min="31" max="31" width="18.5583333333333" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:36" s="1" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="1" s="1" customFormat="1" spans="1:31">
       <c r="A1" s="4" t="s">
         <v>0</v>
       </c>
       <c r="B1" s="4" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="9" t="s">
+      <c r="C1" s="10" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="5" t="s">
+      <c r="D1" s="4" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="5" t="s">
+      <c r="E1" s="4" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="5" t="s">
+      <c r="F1" s="4" t="s">
         <v>5</v>
       </c>
       <c r="G1" s="4" t="s">
@@ -628,99 +1298,145 @@
       <c r="Q1" s="4" t="s">
         <v>16</v>
       </c>
-      <c r="R1"/>
-      <c r="S1"/>
-      <c r="T1"/>
-      <c r="U1"/>
-      <c r="V1"/>
-      <c r="W1"/>
-      <c r="X1"/>
-      <c r="Y1"/>
-      <c r="Z1"/>
-      <c r="AA1"/>
-      <c r="AB1"/>
-      <c r="AC1"/>
-      <c r="AD1"/>
-      <c r="AE1"/>
-      <c r="AF1"/>
-      <c r="AG1"/>
-      <c r="AH1"/>
-      <c r="AI1"/>
-      <c r="AJ1"/>
+      <c r="R1" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="S1" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="T1" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="U1" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="V1" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="W1" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="X1" s="4" t="s">
+        <v>23</v>
+      </c>
+      <c r="Y1" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="Z1" s="4" t="s">
+        <v>25</v>
+      </c>
+      <c r="AA1" s="4" t="s">
+        <v>26</v>
+      </c>
+      <c r="AB1" s="4" t="s">
+        <v>27</v>
+      </c>
+      <c r="AC1" s="4" t="s">
+        <v>28</v>
+      </c>
+      <c r="AD1" s="4" t="s">
+        <v>29</v>
+      </c>
+      <c r="AE1" s="4" t="s">
+        <v>30</v>
+      </c>
     </row>
-    <row r="2" spans="1:36" s="2" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="2" s="2" customFormat="1" spans="1:31">
       <c r="A2" s="6" t="s">
-        <v>17</v>
+        <v>31</v>
       </c>
       <c r="B2" s="6" t="s">
-        <v>18</v>
-      </c>
-      <c r="C2" s="10"/>
+        <v>32</v>
+      </c>
+      <c r="C2" s="11"/>
       <c r="D2" s="6" t="s">
-        <v>19</v>
+        <v>33</v>
       </c>
       <c r="E2" s="6" t="s">
-        <v>19</v>
+        <v>33</v>
       </c>
       <c r="F2" s="6" t="s">
-        <v>19</v>
+        <v>33</v>
       </c>
       <c r="G2" s="6" t="s">
-        <v>20</v>
+        <v>34</v>
       </c>
       <c r="H2" s="6" t="s">
-        <v>20</v>
+        <v>34</v>
       </c>
       <c r="I2" s="6" t="s">
-        <v>20</v>
+        <v>34</v>
       </c>
       <c r="J2" s="6" t="s">
-        <v>21</v>
+        <v>35</v>
       </c>
       <c r="K2" s="6" t="s">
-        <v>21</v>
+        <v>35</v>
       </c>
       <c r="L2" s="6" t="s">
-        <v>20</v>
+        <v>34</v>
       </c>
       <c r="M2" s="6" t="s">
-        <v>20</v>
+        <v>34</v>
       </c>
       <c r="N2" s="6" t="s">
-        <v>20</v>
+        <v>34</v>
       </c>
       <c r="O2" s="6" t="s">
-        <v>20</v>
+        <v>34</v>
       </c>
       <c r="P2" s="6" t="s">
-        <v>20</v>
+        <v>34</v>
       </c>
       <c r="Q2" s="6" t="s">
-        <v>20</v>
-      </c>
-      <c r="R2"/>
-      <c r="S2"/>
-      <c r="T2"/>
-      <c r="U2"/>
-      <c r="V2"/>
-      <c r="W2"/>
-      <c r="X2"/>
-      <c r="Y2"/>
-      <c r="Z2"/>
-      <c r="AA2"/>
-      <c r="AB2"/>
-      <c r="AC2"/>
-      <c r="AD2"/>
-      <c r="AE2"/>
-      <c r="AF2"/>
-      <c r="AG2"/>
-      <c r="AH2"/>
-      <c r="AI2"/>
-      <c r="AJ2"/>
+        <v>34</v>
+      </c>
+      <c r="R2" s="6" t="s">
+        <v>34</v>
+      </c>
+      <c r="S2" s="6" t="s">
+        <v>36</v>
+      </c>
+      <c r="T2" s="6" t="s">
+        <v>36</v>
+      </c>
+      <c r="U2" s="6" t="s">
+        <v>34</v>
+      </c>
+      <c r="V2" s="6" t="s">
+        <v>34</v>
+      </c>
+      <c r="W2" s="6" t="s">
+        <v>34</v>
+      </c>
+      <c r="X2" s="6" t="s">
+        <v>34</v>
+      </c>
+      <c r="Y2" s="6" t="s">
+        <v>34</v>
+      </c>
+      <c r="Z2" s="6" t="s">
+        <v>34</v>
+      </c>
+      <c r="AA2" s="6" t="s">
+        <v>34</v>
+      </c>
+      <c r="AB2" s="6" t="s">
+        <v>34</v>
+      </c>
+      <c r="AC2" s="6" t="s">
+        <v>34</v>
+      </c>
+      <c r="AD2" s="6" t="s">
+        <v>34</v>
+      </c>
+      <c r="AE2" s="6" t="s">
+        <v>32</v>
+      </c>
     </row>
-    <row r="3" spans="1:36" s="2" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="3" s="2" customFormat="1" spans="1:31">
       <c r="A3" s="6" t="s">
-        <v>22</v>
+        <v>37</v>
       </c>
       <c r="B3" s="6"/>
       <c r="C3" s="11"/>
@@ -738,291 +1454,709 @@
       <c r="O3" s="6"/>
       <c r="P3" s="6"/>
       <c r="Q3" s="6"/>
-      <c r="R3"/>
-      <c r="S3"/>
-      <c r="T3"/>
-      <c r="U3"/>
-      <c r="V3"/>
-      <c r="W3"/>
-      <c r="X3"/>
-      <c r="Y3"/>
-      <c r="Z3"/>
-      <c r="AA3"/>
-      <c r="AB3"/>
-      <c r="AC3"/>
-      <c r="AD3"/>
-      <c r="AE3"/>
-      <c r="AF3"/>
-      <c r="AG3"/>
-      <c r="AH3"/>
-      <c r="AI3"/>
-      <c r="AJ3"/>
+      <c r="R3" s="6"/>
+      <c r="S3" s="6"/>
+      <c r="T3" s="6"/>
+      <c r="U3" s="6"/>
+      <c r="V3" s="6"/>
+      <c r="W3" s="6" t="s">
+        <v>38</v>
+      </c>
+      <c r="X3" s="6" t="s">
+        <v>38</v>
+      </c>
+      <c r="Y3" s="6" t="s">
+        <v>38</v>
+      </c>
+      <c r="Z3" s="6" t="s">
+        <v>38</v>
+      </c>
+      <c r="AA3" s="6" t="s">
+        <v>38</v>
+      </c>
+      <c r="AB3" s="6"/>
+      <c r="AC3" s="6" t="s">
+        <v>38</v>
+      </c>
+      <c r="AD3" s="6" t="s">
+        <v>38</v>
+      </c>
+      <c r="AE3" s="6"/>
     </row>
-    <row r="4" spans="1:36" s="1" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="4" s="1" customFormat="1" spans="1:31">
       <c r="A4" s="4" t="s">
-        <v>23</v>
-      </c>
-      <c r="B4" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="C4" s="9" t="s">
-        <v>25</v>
-      </c>
-      <c r="D4" s="5" t="s">
-        <v>26</v>
-      </c>
-      <c r="E4" s="5" t="s">
-        <v>27</v>
-      </c>
-      <c r="F4" s="5" t="s">
-        <v>28</v>
+        <v>39</v>
+      </c>
+      <c r="B4" s="4" t="s">
+        <v>40</v>
+      </c>
+      <c r="C4" s="10" t="s">
+        <v>41</v>
+      </c>
+      <c r="D4" s="4" t="s">
+        <v>42</v>
+      </c>
+      <c r="E4" s="4" t="s">
+        <v>43</v>
+      </c>
+      <c r="F4" s="4" t="s">
+        <v>44</v>
       </c>
       <c r="G4" s="4" t="s">
-        <v>29</v>
+        <v>45</v>
       </c>
       <c r="H4" s="4" t="s">
-        <v>30</v>
+        <v>46</v>
       </c>
       <c r="I4" s="4" t="s">
-        <v>31</v>
+        <v>47</v>
       </c>
       <c r="J4" s="4" t="s">
-        <v>32</v>
+        <v>48</v>
       </c>
       <c r="K4" s="4" t="s">
-        <v>33</v>
+        <v>49</v>
       </c>
       <c r="L4" s="4" t="s">
-        <v>34</v>
+        <v>50</v>
       </c>
       <c r="M4" s="4" t="s">
-        <v>35</v>
+        <v>51</v>
       </c>
       <c r="N4" s="4" t="s">
-        <v>36</v>
+        <v>52</v>
       </c>
       <c r="O4" s="4" t="s">
-        <v>37</v>
+        <v>53</v>
       </c>
       <c r="P4" s="4" t="s">
-        <v>38</v>
+        <v>54</v>
       </c>
       <c r="Q4" s="4" t="s">
-        <v>39</v>
-      </c>
-      <c r="R4"/>
-      <c r="S4"/>
-      <c r="T4"/>
-      <c r="U4"/>
-      <c r="V4"/>
-      <c r="W4"/>
-      <c r="X4"/>
-      <c r="Y4"/>
-      <c r="Z4"/>
-      <c r="AA4"/>
-      <c r="AB4"/>
-      <c r="AC4"/>
-      <c r="AD4"/>
-      <c r="AE4"/>
-      <c r="AF4"/>
-      <c r="AG4"/>
-      <c r="AH4"/>
-      <c r="AI4"/>
-      <c r="AJ4"/>
+        <v>55</v>
+      </c>
+      <c r="R4" s="4" t="s">
+        <v>56</v>
+      </c>
+      <c r="S4" s="4" t="s">
+        <v>57</v>
+      </c>
+      <c r="T4" s="4" t="s">
+        <v>58</v>
+      </c>
+      <c r="U4" s="4" t="s">
+        <v>59</v>
+      </c>
+      <c r="V4" s="4" t="s">
+        <v>60</v>
+      </c>
+      <c r="W4" s="4" t="s">
+        <v>61</v>
+      </c>
+      <c r="X4" s="4" t="s">
+        <v>62</v>
+      </c>
+      <c r="Y4" s="4" t="s">
+        <v>63</v>
+      </c>
+      <c r="Z4" s="4" t="s">
+        <v>64</v>
+      </c>
+      <c r="AA4" s="4" t="s">
+        <v>65</v>
+      </c>
+      <c r="AB4" s="4" t="s">
+        <v>66</v>
+      </c>
+      <c r="AC4" s="4" t="s">
+        <v>67</v>
+      </c>
+      <c r="AD4" s="4" t="s">
+        <v>68</v>
+      </c>
+      <c r="AE4" s="4" t="s">
+        <v>69</v>
+      </c>
     </row>
-    <row r="5" spans="1:36" x14ac:dyDescent="0.3">
-      <c r="A5" s="7"/>
-      <c r="B5" s="7"/>
-      <c r="C5" s="12"/>
-      <c r="D5" s="8"/>
-      <c r="E5" s="8"/>
-      <c r="F5" s="8"/>
-      <c r="G5" s="7"/>
-      <c r="H5" s="7"/>
-      <c r="I5" s="7"/>
-      <c r="J5" s="7"/>
-      <c r="K5" s="7"/>
-      <c r="L5" s="7"/>
-      <c r="M5" s="7"/>
-      <c r="N5" s="7"/>
-      <c r="O5" s="7"/>
-      <c r="P5" s="7"/>
-      <c r="Q5" s="7"/>
+    <row r="5" spans="1:31">
+      <c r="A5" s="12"/>
+      <c r="B5" s="12"/>
+      <c r="C5" s="13"/>
+      <c r="D5" s="12"/>
+      <c r="E5" s="12"/>
+      <c r="F5" s="12"/>
+      <c r="G5" s="12"/>
+      <c r="H5" s="12"/>
+      <c r="I5" s="12"/>
+      <c r="J5" s="12"/>
+      <c r="K5" s="12"/>
+      <c r="L5" s="12"/>
+      <c r="M5" s="12"/>
+      <c r="N5" s="12"/>
+      <c r="O5" s="12"/>
+      <c r="P5" s="12"/>
+      <c r="Q5" s="12"/>
+      <c r="R5" s="12"/>
     </row>
-    <row r="6" spans="1:36" x14ac:dyDescent="0.3">
-      <c r="A6" s="7"/>
-      <c r="B6" s="7"/>
-      <c r="C6" s="12"/>
-      <c r="D6" s="8"/>
-      <c r="E6" s="8"/>
-      <c r="F6" s="8"/>
-      <c r="G6" s="7"/>
-      <c r="H6" s="7"/>
-      <c r="I6" s="7"/>
-      <c r="J6" s="7"/>
-      <c r="K6" s="7"/>
-      <c r="L6" s="7"/>
-      <c r="M6" s="7"/>
-      <c r="N6" s="7"/>
-      <c r="O6" s="7"/>
-      <c r="P6" s="7"/>
-      <c r="Q6" s="7"/>
+    <row r="6" spans="1:31">
+      <c r="A6" s="12"/>
+      <c r="B6" s="12"/>
+      <c r="C6" s="13"/>
+      <c r="D6" s="12"/>
+      <c r="E6" s="12"/>
+      <c r="F6" s="12"/>
+      <c r="G6" s="12"/>
+      <c r="H6" s="12"/>
+      <c r="I6" s="12"/>
+      <c r="J6" s="12"/>
+      <c r="K6" s="12"/>
+      <c r="L6" s="12"/>
+      <c r="M6" s="12"/>
+      <c r="N6" s="12"/>
+      <c r="O6" s="12"/>
+      <c r="P6" s="12"/>
+      <c r="Q6" s="12"/>
+      <c r="R6" s="12"/>
     </row>
-    <row r="7" spans="1:36" x14ac:dyDescent="0.3">
-      <c r="A7" s="7"/>
-      <c r="B7" s="7"/>
-      <c r="C7" s="12"/>
-      <c r="D7" s="8"/>
-      <c r="E7" s="8"/>
-      <c r="F7" s="8"/>
-      <c r="G7" s="7"/>
-      <c r="H7" s="7"/>
-      <c r="I7" s="7"/>
-      <c r="J7" s="7"/>
-      <c r="K7" s="7"/>
-      <c r="L7" s="7"/>
-      <c r="M7" s="7"/>
-      <c r="N7" s="7"/>
-      <c r="O7" s="7"/>
-      <c r="P7" s="7"/>
-      <c r="Q7" s="7"/>
+    <row r="7" spans="1:31">
+      <c r="A7" s="12"/>
+      <c r="B7" s="12"/>
+      <c r="C7" s="13"/>
+      <c r="D7" s="12"/>
+      <c r="E7" s="12"/>
+      <c r="F7" s="12"/>
+      <c r="G7" s="12"/>
+      <c r="H7" s="12"/>
+      <c r="I7" s="12"/>
+      <c r="J7" s="12"/>
+      <c r="K7" s="12"/>
+      <c r="L7" s="12"/>
+      <c r="M7" s="12"/>
+      <c r="N7" s="12"/>
+      <c r="O7" s="12"/>
+      <c r="P7" s="12"/>
+      <c r="Q7" s="12"/>
+      <c r="R7" s="12"/>
     </row>
-    <row r="8" spans="1:36" x14ac:dyDescent="0.3">
-      <c r="A8" s="7"/>
-      <c r="B8" s="7"/>
+    <row r="8" spans="1:31">
+      <c r="A8" s="12"/>
+      <c r="B8" s="12"/>
       <c r="C8" s="13"/>
-      <c r="D8" s="7"/>
-      <c r="E8" s="7"/>
-      <c r="F8" s="7"/>
-      <c r="G8" s="7"/>
-      <c r="H8" s="7"/>
-      <c r="I8" s="7"/>
-      <c r="J8" s="7"/>
-      <c r="K8" s="7"/>
-      <c r="L8" s="7"/>
-      <c r="M8" s="7"/>
-      <c r="N8" s="7"/>
-      <c r="O8" s="7"/>
-      <c r="P8" s="7"/>
-      <c r="Q8" s="7"/>
+      <c r="D8" s="12"/>
+      <c r="E8" s="12"/>
+      <c r="F8" s="12"/>
+      <c r="G8" s="12"/>
+      <c r="H8" s="12"/>
+      <c r="I8" s="12"/>
+      <c r="J8" s="12"/>
+      <c r="K8" s="12"/>
+      <c r="L8" s="12"/>
+      <c r="M8" s="12"/>
+      <c r="N8" s="12"/>
+      <c r="O8" s="12"/>
+      <c r="P8" s="12"/>
+      <c r="Q8" s="12"/>
+      <c r="R8" s="12"/>
     </row>
-    <row r="9" spans="1:36" x14ac:dyDescent="0.3">
-      <c r="A9" s="7"/>
-      <c r="B9" s="7"/>
+    <row r="9" spans="1:31">
+      <c r="A9" s="12"/>
+      <c r="B9" s="12"/>
       <c r="C9" s="13"/>
-      <c r="D9" s="7"/>
-      <c r="E9" s="7"/>
-      <c r="F9" s="7"/>
-      <c r="G9" s="7"/>
-      <c r="H9" s="7"/>
-      <c r="I9" s="7"/>
-      <c r="J9" s="7"/>
-      <c r="K9" s="7"/>
-      <c r="L9" s="7"/>
-      <c r="M9" s="7"/>
-      <c r="N9" s="7"/>
-      <c r="O9" s="7"/>
-      <c r="P9" s="7"/>
-      <c r="Q9" s="7"/>
+      <c r="D9" s="12"/>
+      <c r="E9" s="12"/>
+      <c r="F9" s="12"/>
+      <c r="G9" s="12"/>
+      <c r="H9" s="12"/>
+      <c r="I9" s="12"/>
+      <c r="J9" s="12"/>
+      <c r="K9" s="12"/>
+      <c r="L9" s="12"/>
+      <c r="M9" s="12"/>
+      <c r="N9" s="12"/>
+      <c r="O9" s="12"/>
+      <c r="P9" s="12"/>
+      <c r="Q9" s="12"/>
+      <c r="R9" s="12"/>
     </row>
-    <row r="10" spans="1:36" x14ac:dyDescent="0.3">
-      <c r="A10" s="7"/>
-      <c r="B10" s="7"/>
+    <row r="10" spans="1:31">
+      <c r="A10" s="12"/>
+      <c r="B10" s="12"/>
       <c r="C10" s="13"/>
-      <c r="D10" s="8"/>
-      <c r="E10" s="8"/>
-      <c r="F10" s="8"/>
-      <c r="G10" s="7"/>
-      <c r="H10" s="7"/>
-      <c r="I10" s="7"/>
-      <c r="J10" s="7"/>
-      <c r="K10" s="7"/>
-      <c r="L10" s="7"/>
-      <c r="M10" s="7"/>
-      <c r="N10" s="7"/>
-      <c r="O10" s="7"/>
-      <c r="P10" s="7"/>
-      <c r="Q10" s="7"/>
+      <c r="D10" s="12"/>
+      <c r="E10" s="12"/>
+      <c r="F10" s="12"/>
+      <c r="G10" s="12"/>
+      <c r="H10" s="12"/>
+      <c r="I10" s="12"/>
+      <c r="J10" s="12"/>
+      <c r="K10" s="12"/>
+      <c r="L10" s="12"/>
+      <c r="M10" s="12"/>
+      <c r="N10" s="12"/>
+      <c r="O10" s="12"/>
+      <c r="P10" s="12"/>
+      <c r="Q10" s="12"/>
+      <c r="R10" s="12"/>
     </row>
-    <row r="11" spans="1:36" x14ac:dyDescent="0.3">
-      <c r="A11" s="7"/>
-      <c r="B11" s="7"/>
+    <row r="11" spans="1:31">
+      <c r="A11" s="12"/>
+      <c r="B11" s="12"/>
       <c r="C11" s="13"/>
-      <c r="D11" s="7"/>
-      <c r="E11" s="7"/>
-      <c r="F11" s="7"/>
-      <c r="G11" s="7"/>
-      <c r="H11" s="7"/>
-      <c r="I11" s="7"/>
-      <c r="J11" s="7"/>
-      <c r="K11" s="7"/>
-      <c r="L11" s="7"/>
-      <c r="M11" s="7"/>
-      <c r="N11" s="7"/>
-      <c r="O11" s="7"/>
-      <c r="P11" s="7"/>
-      <c r="Q11" s="7"/>
+      <c r="D11" s="12"/>
+      <c r="E11" s="12"/>
+      <c r="F11" s="12"/>
+      <c r="G11" s="12"/>
+      <c r="H11" s="12"/>
+      <c r="I11" s="12"/>
+      <c r="J11" s="12"/>
+      <c r="K11" s="12"/>
+      <c r="L11" s="12"/>
+      <c r="M11" s="12"/>
+      <c r="N11" s="12"/>
+      <c r="O11" s="12"/>
+      <c r="P11" s="12"/>
+      <c r="Q11" s="12"/>
+      <c r="R11" s="12"/>
     </row>
-    <row r="12" spans="1:36" x14ac:dyDescent="0.3">
-      <c r="A12" s="7"/>
-      <c r="B12" s="7"/>
-      <c r="C12" s="12"/>
-      <c r="D12" s="8"/>
-      <c r="E12" s="8"/>
-      <c r="F12" s="8"/>
-      <c r="G12" s="7"/>
-      <c r="H12" s="7"/>
-      <c r="I12" s="7"/>
-      <c r="J12" s="7"/>
-      <c r="K12" s="7"/>
-      <c r="L12" s="7"/>
-      <c r="M12" s="7"/>
-      <c r="N12" s="7"/>
-      <c r="O12" s="7"/>
-      <c r="P12" s="7"/>
-      <c r="Q12" s="7"/>
+    <row r="12" spans="1:31">
+      <c r="A12" s="12"/>
+      <c r="B12" s="12"/>
+      <c r="C12" s="13"/>
+      <c r="D12" s="12"/>
+      <c r="E12" s="12"/>
+      <c r="F12" s="12"/>
+      <c r="G12" s="12"/>
+      <c r="H12" s="12"/>
+      <c r="I12" s="12"/>
+      <c r="J12" s="12"/>
+      <c r="K12" s="12"/>
+      <c r="L12" s="12"/>
+      <c r="M12" s="12"/>
+      <c r="N12" s="12"/>
+      <c r="O12" s="12"/>
+      <c r="P12" s="12"/>
+      <c r="Q12" s="12"/>
+      <c r="R12" s="12"/>
     </row>
-    <row r="13" spans="1:36" x14ac:dyDescent="0.3">
-      <c r="A13" s="7"/>
-      <c r="B13" s="7"/>
-      <c r="C13" s="12"/>
-      <c r="D13" s="8"/>
-      <c r="E13" s="8"/>
-      <c r="F13" s="8"/>
-      <c r="G13" s="7"/>
-      <c r="H13" s="7"/>
-      <c r="I13" s="7"/>
-      <c r="J13" s="7"/>
-      <c r="K13" s="7"/>
-      <c r="L13" s="7"/>
-      <c r="M13" s="7"/>
-      <c r="N13" s="7"/>
-      <c r="O13" s="7"/>
-      <c r="P13" s="7"/>
-      <c r="Q13" s="7"/>
+    <row r="13" spans="1:31">
+      <c r="A13" s="12"/>
+      <c r="B13" s="12"/>
+      <c r="C13" s="13"/>
+      <c r="D13" s="12"/>
+      <c r="E13" s="12"/>
+      <c r="F13" s="12"/>
+      <c r="G13" s="12"/>
+      <c r="H13" s="12"/>
+      <c r="I13" s="12"/>
+      <c r="J13" s="12"/>
+      <c r="K13" s="12"/>
+      <c r="L13" s="12"/>
+      <c r="M13" s="12"/>
+      <c r="N13" s="12"/>
+      <c r="O13" s="12"/>
+      <c r="P13" s="12"/>
+      <c r="Q13" s="12"/>
+      <c r="R13" s="12"/>
     </row>
-    <row r="14" spans="1:36" x14ac:dyDescent="0.3">
-      <c r="A14" s="7"/>
-      <c r="B14" s="7"/>
-      <c r="C14" s="12"/>
-      <c r="D14" s="8"/>
-      <c r="E14" s="8"/>
-      <c r="F14" s="8"/>
-      <c r="G14" s="7"/>
-      <c r="H14" s="7"/>
-      <c r="I14" s="7"/>
-      <c r="J14" s="7"/>
-      <c r="K14" s="7"/>
-      <c r="L14" s="7"/>
-      <c r="M14" s="7"/>
-      <c r="N14" s="7"/>
-      <c r="O14" s="7"/>
-      <c r="P14" s="7"/>
-      <c r="Q14" s="7"/>
+    <row r="14" spans="1:31">
+      <c r="A14" s="12"/>
+      <c r="B14" s="12"/>
+      <c r="C14" s="13"/>
+      <c r="D14" s="12"/>
+      <c r="E14" s="12"/>
+      <c r="F14" s="12"/>
+      <c r="G14" s="12"/>
+      <c r="H14" s="12"/>
+      <c r="I14" s="12"/>
+      <c r="J14" s="12"/>
+      <c r="K14" s="12"/>
+      <c r="L14" s="12"/>
+      <c r="M14" s="12"/>
+      <c r="N14" s="12"/>
+      <c r="O14" s="12"/>
+      <c r="P14" s="12"/>
+      <c r="Q14" s="12"/>
+      <c r="R14" s="12"/>
     </row>
   </sheetData>
-  <phoneticPr fontId="3" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait"/>
+  <headerFooter/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
+  <dimension ref="A1:AE4"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25" outlineLevelRow="3"/>
+  <cols>
+    <col min="2" max="2" width="12.625" customWidth="1"/>
+    <col min="3" max="3" width="15.375" style="3" customWidth="1"/>
+    <col min="4" max="4" width="26.625" customWidth="1"/>
+    <col min="5" max="5" width="23.5" customWidth="1"/>
+    <col min="6" max="6" width="18" customWidth="1"/>
+    <col min="7" max="7" width="19.625" customWidth="1"/>
+    <col min="8" max="8" width="19.5" customWidth="1"/>
+    <col min="9" max="9" width="21.625" customWidth="1"/>
+    <col min="10" max="10" width="14.125" customWidth="1"/>
+    <col min="11" max="11" width="18.75" customWidth="1"/>
+    <col min="12" max="12" width="23.875" customWidth="1"/>
+    <col min="13" max="13" width="20.875" customWidth="1"/>
+    <col min="14" max="14" width="19.75" customWidth="1"/>
+    <col min="15" max="15" width="17.25" customWidth="1"/>
+    <col min="16" max="16" width="24.375" customWidth="1"/>
+    <col min="17" max="17" width="23.5" customWidth="1"/>
+    <col min="18" max="18" width="27.375" customWidth="1"/>
+    <col min="19" max="19" width="25.125" customWidth="1"/>
+    <col min="20" max="20" width="24.875" customWidth="1"/>
+    <col min="21" max="21" width="19.25" customWidth="1"/>
+    <col min="22" max="22" width="23.875" customWidth="1"/>
+    <col min="23" max="23" width="20.75" customWidth="1"/>
+    <col min="24" max="24" width="20.125" customWidth="1"/>
+    <col min="25" max="25" width="22.625" customWidth="1"/>
+    <col min="26" max="26" width="20.125" customWidth="1"/>
+    <col min="27" max="27" width="24.75" customWidth="1"/>
+    <col min="28" max="28" width="27" customWidth="1"/>
+    <col min="29" max="29" width="25.875" customWidth="1"/>
+    <col min="30" max="30" width="28.25" customWidth="1"/>
+    <col min="31" max="31" width="22.75" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" s="1" customFormat="1" spans="1:31">
+      <c r="A1" s="4" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="4" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="5" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="4" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="G1" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="H1" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="I1" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="J1" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="K1" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="L1" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="M1" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="N1" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="O1" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="P1" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="Q1" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="R1" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="S1" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="T1" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="U1" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="V1" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="W1" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="X1" s="4" t="s">
+        <v>23</v>
+      </c>
+      <c r="Y1" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="Z1" s="4" t="s">
+        <v>25</v>
+      </c>
+      <c r="AA1" s="4" t="s">
+        <v>26</v>
+      </c>
+      <c r="AB1" s="4" t="s">
+        <v>27</v>
+      </c>
+      <c r="AC1" s="4" t="s">
+        <v>28</v>
+      </c>
+      <c r="AD1" s="4" t="s">
+        <v>29</v>
+      </c>
+      <c r="AE1" s="4" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="2" s="2" customFormat="1" spans="1:31">
+      <c r="A2" s="6" t="s">
+        <v>31</v>
+      </c>
+      <c r="B2" s="6" t="s">
+        <v>32</v>
+      </c>
+      <c r="C2" s="7"/>
+      <c r="D2" s="6" t="s">
+        <v>33</v>
+      </c>
+      <c r="E2" s="6" t="s">
+        <v>33</v>
+      </c>
+      <c r="F2" s="6" t="s">
+        <v>33</v>
+      </c>
+      <c r="G2" s="6" t="s">
+        <v>34</v>
+      </c>
+      <c r="H2" s="6" t="s">
+        <v>34</v>
+      </c>
+      <c r="I2" s="6" t="s">
+        <v>34</v>
+      </c>
+      <c r="J2" s="6" t="s">
+        <v>35</v>
+      </c>
+      <c r="K2" s="6" t="s">
+        <v>35</v>
+      </c>
+      <c r="L2" s="6" t="s">
+        <v>34</v>
+      </c>
+      <c r="M2" s="6" t="s">
+        <v>34</v>
+      </c>
+      <c r="N2" s="6" t="s">
+        <v>34</v>
+      </c>
+      <c r="O2" s="6" t="s">
+        <v>34</v>
+      </c>
+      <c r="P2" s="6" t="s">
+        <v>34</v>
+      </c>
+      <c r="Q2" s="6" t="s">
+        <v>34</v>
+      </c>
+      <c r="R2" s="6" t="s">
+        <v>34</v>
+      </c>
+      <c r="S2" s="6" t="s">
+        <v>36</v>
+      </c>
+      <c r="T2" s="6" t="s">
+        <v>36</v>
+      </c>
+      <c r="U2" s="6" t="s">
+        <v>34</v>
+      </c>
+      <c r="V2" s="6" t="s">
+        <v>34</v>
+      </c>
+      <c r="W2" s="6" t="s">
+        <v>34</v>
+      </c>
+      <c r="X2" s="6" t="s">
+        <v>34</v>
+      </c>
+      <c r="Y2" s="6" t="s">
+        <v>34</v>
+      </c>
+      <c r="Z2" s="6" t="s">
+        <v>34</v>
+      </c>
+      <c r="AA2" s="6" t="s">
+        <v>34</v>
+      </c>
+      <c r="AB2" s="6" t="s">
+        <v>34</v>
+      </c>
+      <c r="AC2" s="6" t="s">
+        <v>34</v>
+      </c>
+      <c r="AD2" s="6" t="s">
+        <v>34</v>
+      </c>
+      <c r="AE2" s="6" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="3" s="2" customFormat="1" spans="1:31">
+      <c r="A3" s="6" t="s">
+        <v>37</v>
+      </c>
+      <c r="B3" s="6"/>
+      <c r="C3" s="7"/>
+      <c r="D3" s="6"/>
+      <c r="E3" s="6"/>
+      <c r="F3" s="6"/>
+      <c r="G3" s="6"/>
+      <c r="H3" s="6"/>
+      <c r="I3" s="6"/>
+      <c r="J3" s="6"/>
+      <c r="K3" s="6"/>
+      <c r="L3" s="6"/>
+      <c r="M3" s="6"/>
+      <c r="N3" s="6"/>
+      <c r="O3" s="6"/>
+      <c r="P3" s="6"/>
+      <c r="Q3" s="6"/>
+      <c r="R3" s="6"/>
+      <c r="S3" s="6"/>
+      <c r="T3" s="6"/>
+      <c r="U3" s="6"/>
+      <c r="V3" s="6"/>
+      <c r="W3" s="6" t="s">
+        <v>38</v>
+      </c>
+      <c r="X3" s="6" t="s">
+        <v>38</v>
+      </c>
+      <c r="Y3" s="6" t="s">
+        <v>38</v>
+      </c>
+      <c r="Z3" s="6" t="s">
+        <v>38</v>
+      </c>
+      <c r="AA3" s="6" t="s">
+        <v>38</v>
+      </c>
+      <c r="AB3" s="6"/>
+      <c r="AC3" s="6" t="s">
+        <v>38</v>
+      </c>
+      <c r="AD3" s="6" t="s">
+        <v>38</v>
+      </c>
+      <c r="AE3" s="6"/>
+    </row>
+    <row r="4" s="1" customFormat="1" spans="1:31">
+      <c r="A4" s="4" t="s">
+        <v>39</v>
+      </c>
+      <c r="B4" s="4" t="s">
+        <v>40</v>
+      </c>
+      <c r="C4" s="5" t="s">
+        <v>41</v>
+      </c>
+      <c r="D4" s="4" t="s">
+        <v>42</v>
+      </c>
+      <c r="E4" s="4" t="s">
+        <v>43</v>
+      </c>
+      <c r="F4" s="4" t="s">
+        <v>44</v>
+      </c>
+      <c r="G4" s="4" t="s">
+        <v>45</v>
+      </c>
+      <c r="H4" s="4" t="s">
+        <v>46</v>
+      </c>
+      <c r="I4" s="4" t="s">
+        <v>47</v>
+      </c>
+      <c r="J4" s="4" t="s">
+        <v>48</v>
+      </c>
+      <c r="K4" s="4" t="s">
+        <v>49</v>
+      </c>
+      <c r="L4" s="4" t="s">
+        <v>50</v>
+      </c>
+      <c r="M4" s="4" t="s">
+        <v>51</v>
+      </c>
+      <c r="N4" s="4" t="s">
+        <v>52</v>
+      </c>
+      <c r="O4" s="4" t="s">
+        <v>53</v>
+      </c>
+      <c r="P4" s="4" t="s">
+        <v>54</v>
+      </c>
+      <c r="Q4" s="4" t="s">
+        <v>55</v>
+      </c>
+      <c r="R4" s="4" t="s">
+        <v>56</v>
+      </c>
+      <c r="S4" s="4" t="s">
+        <v>57</v>
+      </c>
+      <c r="T4" s="4" t="s">
+        <v>58</v>
+      </c>
+      <c r="U4" s="4" t="s">
+        <v>59</v>
+      </c>
+      <c r="V4" s="4" t="s">
+        <v>60</v>
+      </c>
+      <c r="W4" s="4" t="s">
+        <v>61</v>
+      </c>
+      <c r="X4" s="4" t="s">
+        <v>62</v>
+      </c>
+      <c r="Y4" s="4" t="s">
+        <v>63</v>
+      </c>
+      <c r="Z4" s="4" t="s">
+        <v>64</v>
+      </c>
+      <c r="AA4" s="4" t="s">
+        <v>65</v>
+      </c>
+      <c r="AB4" s="4" t="s">
+        <v>66</v>
+      </c>
+      <c r="AC4" s="4" t="s">
+        <v>67</v>
+      </c>
+      <c r="AD4" s="4" t="s">
+        <v>68</v>
+      </c>
+      <c r="AE4" s="4" t="s">
+        <v>69</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <headerFooter/>
 </worksheet>
 </file>
--- a/GameConfig/Datas/模型/模型配置表.xlsx
+++ b/GameConfig/Datas/模型/模型配置表.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowHeight="17655"/>
+    <workbookView windowHeight="17680"/>
   </bookViews>
   <sheets>
     <sheet name="角色模型配置表" sheetId="1" r:id="rId1"/>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="200" uniqueCount="70">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="200" uniqueCount="72">
   <si>
     <t>##var</t>
   </si>
@@ -90,154 +90,160 @@
     <t>UseAabbCollision</t>
   </si>
   <si>
+    <t>CapsuleRadius</t>
+  </si>
+  <si>
+    <t>CapsuleHeight</t>
+  </si>
+  <si>
+    <t>HpBarOffsetX</t>
+  </si>
+  <si>
+    <t>HpBarOffsetY</t>
+  </si>
+  <si>
+    <t>HitFlashColorR</t>
+  </si>
+  <si>
+    <t>HitFlashColorG</t>
+  </si>
+  <si>
+    <t>HitFlashColorB</t>
+  </si>
+  <si>
+    <t>HitFullFlashTime</t>
+  </si>
+  <si>
+    <t>HitFlashTime</t>
+  </si>
+  <si>
+    <t>DeathFadeOutDurTime</t>
+  </si>
+  <si>
+    <t>DeathEffectSoundID</t>
+  </si>
+  <si>
+    <t>##type</t>
+  </si>
+  <si>
+    <t>int</t>
+  </si>
+  <si>
+    <t>string</t>
+  </si>
+  <si>
+    <t>float</t>
+  </si>
+  <si>
+    <t>byte</t>
+  </si>
+  <si>
+    <t>bool</t>
+  </si>
+  <si>
+    <t>##group</t>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t>##</t>
+  </si>
+  <si>
+    <t>模型ID</t>
+  </si>
+  <si>
+    <t>备注内容</t>
+  </si>
+  <si>
+    <t>UISpine可寻址地址</t>
+  </si>
+  <si>
+    <t>Model可寻址地址</t>
+  </si>
+  <si>
+    <t>帧动画配置文件</t>
+  </si>
+  <si>
+    <t>死亡动画速度</t>
+  </si>
+  <si>
+    <t>模型缩放</t>
+  </si>
+  <si>
+    <t>UI模型缩放</t>
+  </si>
+  <si>
+    <t>显示类型</t>
+  </si>
+  <si>
+    <t>显示阴影</t>
+  </si>
+  <si>
+    <t>阴影宽度</t>
+  </si>
+  <si>
+    <t>阴影高度</t>
+  </si>
+  <si>
+    <t>阴影缩放X</t>
+  </si>
+  <si>
+    <t>阴影缩放Y</t>
+  </si>
+  <si>
+    <t>阴影偏移X</t>
+  </si>
+  <si>
+    <t>阴影偏移Y</t>
+  </si>
+  <si>
+    <t>参考移动速度</t>
+  </si>
+  <si>
+    <t>是否开启碰撞</t>
+  </si>
+  <si>
+    <t>是否矩形碰撞</t>
+  </si>
+  <si>
+    <t>碰撞半径</t>
+  </si>
+  <si>
+    <t>碰撞高度</t>
+  </si>
+  <si>
+    <t>血条高度偏移X</t>
+  </si>
+  <si>
+    <t>血条高度偏移Y</t>
+  </si>
+  <si>
+    <t>受击高亮R</t>
+  </si>
+  <si>
+    <t>受击高亮G</t>
+  </si>
+  <si>
+    <t>受击高亮B</t>
+  </si>
+  <si>
+    <t>受击高亮总持续时间</t>
+  </si>
+  <si>
+    <t>受击高亮持续时间</t>
+  </si>
+  <si>
+    <t>死亡渐变消失时间</t>
+  </si>
+  <si>
+    <t>死亡音效ID</t>
+  </si>
+  <si>
     <t>CollisionRadius</t>
   </si>
   <si>
     <t>CollisionHeight</t>
-  </si>
-  <si>
-    <t>HpBarOffsetX</t>
-  </si>
-  <si>
-    <t>HpBarOffsetY</t>
-  </si>
-  <si>
-    <t>HitFlashColorR</t>
-  </si>
-  <si>
-    <t>HitFlashColorG</t>
-  </si>
-  <si>
-    <t>HitFlashColorB</t>
-  </si>
-  <si>
-    <t>HitFullFlashTime</t>
-  </si>
-  <si>
-    <t>HitFlashTime</t>
-  </si>
-  <si>
-    <t>DeathFadeOutDurTime</t>
-  </si>
-  <si>
-    <t>DeathEffectSoundID</t>
-  </si>
-  <si>
-    <t>##type</t>
-  </si>
-  <si>
-    <t>int</t>
-  </si>
-  <si>
-    <t>string</t>
-  </si>
-  <si>
-    <t>float</t>
-  </si>
-  <si>
-    <t>byte</t>
-  </si>
-  <si>
-    <t>bool</t>
-  </si>
-  <si>
-    <t>##group</t>
-  </si>
-  <si>
-    <t/>
-  </si>
-  <si>
-    <t>##</t>
-  </si>
-  <si>
-    <t>模型ID</t>
-  </si>
-  <si>
-    <t>备注内容</t>
-  </si>
-  <si>
-    <t>UISpine可寻址地址</t>
-  </si>
-  <si>
-    <t>Model可寻址地址</t>
-  </si>
-  <si>
-    <t>帧动画配置文件</t>
-  </si>
-  <si>
-    <t>死亡动画速度</t>
-  </si>
-  <si>
-    <t>模型缩放</t>
-  </si>
-  <si>
-    <t>UI模型缩放</t>
-  </si>
-  <si>
-    <t>显示类型</t>
-  </si>
-  <si>
-    <t>显示阴影</t>
-  </si>
-  <si>
-    <t>阴影宽度</t>
-  </si>
-  <si>
-    <t>阴影高度</t>
-  </si>
-  <si>
-    <t>阴影缩放X</t>
-  </si>
-  <si>
-    <t>阴影缩放Y</t>
-  </si>
-  <si>
-    <t>阴影偏移X</t>
-  </si>
-  <si>
-    <t>阴影偏移Y</t>
-  </si>
-  <si>
-    <t>参考移动速度</t>
-  </si>
-  <si>
-    <t>是否开启碰撞</t>
-  </si>
-  <si>
-    <t>是否矩形碰撞</t>
-  </si>
-  <si>
-    <t>碰撞半径</t>
-  </si>
-  <si>
-    <t>碰撞高度</t>
-  </si>
-  <si>
-    <t>血条高度偏移X</t>
-  </si>
-  <si>
-    <t>血条高度偏移Y</t>
-  </si>
-  <si>
-    <t>受击高亮R</t>
-  </si>
-  <si>
-    <t>受击高亮G</t>
-  </si>
-  <si>
-    <t>受击高亮B</t>
-  </si>
-  <si>
-    <t>受击高亮总持续时间</t>
-  </si>
-  <si>
-    <t>受击高亮持续时间</t>
-  </si>
-  <si>
-    <t>死亡渐变消失时间</t>
-  </si>
-  <si>
-    <t>死亡音效ID</t>
   </si>
 </sst>
 </file>
@@ -1225,7 +1231,7 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A1:AE14"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14"/>
   <cols>
     <col min="1" max="1" width="9.25" customWidth="1"/>
     <col min="2" max="2" width="17.3333333333333" customWidth="1"/>
@@ -1789,7 +1795,7 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A1:AE4"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25" outlineLevelRow="3"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14" outlineLevelRow="3"/>
   <cols>
     <col min="2" max="2" width="12.625" customWidth="1"/>
     <col min="3" max="3" width="15.375" style="3" customWidth="1"/>
@@ -1885,10 +1891,10 @@
         <v>19</v>
       </c>
       <c r="U1" s="4" t="s">
-        <v>20</v>
+        <v>70</v>
       </c>
       <c r="V1" s="4" t="s">
-        <v>21</v>
+        <v>71</v>
       </c>
       <c r="W1" s="4" t="s">
         <v>22</v>

--- a/GameConfig/Datas/模型/模型配置表.xlsx
+++ b/GameConfig/Datas/模型/模型配置表.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowHeight="17680"/>
+    <workbookView windowHeight="17655"/>
   </bookViews>
   <sheets>
     <sheet name="角色模型配置表" sheetId="1" r:id="rId1"/>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="200" uniqueCount="72">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="283" uniqueCount="91">
   <si>
     <t>##var</t>
   </si>
@@ -123,6 +123,21 @@
     <t>DeathEffectSoundID</t>
   </si>
   <si>
+    <t>WeaponModelBaseParam</t>
+  </si>
+  <si>
+    <t>UIWeaponModelBaseParam</t>
+  </si>
+  <si>
+    <t>UIStandbyAction</t>
+  </si>
+  <si>
+    <t>WeaponOffsetX</t>
+  </si>
+  <si>
+    <t>WeaponOffsetY</t>
+  </si>
+  <si>
     <t>##type</t>
   </si>
   <si>
@@ -141,12 +156,12 @@
     <t>bool</t>
   </si>
   <si>
+    <t/>
+  </si>
+  <si>
     <t>##group</t>
   </si>
   <si>
-    <t/>
-  </si>
-  <si>
     <t>##</t>
   </si>
   <si>
@@ -240,10 +255,52 @@
     <t>死亡音效ID</t>
   </si>
   <si>
-    <t>CollisionRadius</t>
-  </si>
-  <si>
-    <t>CollisionHeight</t>
+    <t>武器基础_偏移X</t>
+  </si>
+  <si>
+    <t>武器基础_偏移Y</t>
+  </si>
+  <si>
+    <t>武器基础_旋转X</t>
+  </si>
+  <si>
+    <t>武器基础_旋转Y</t>
+  </si>
+  <si>
+    <t>武器基础_旋转Z</t>
+  </si>
+  <si>
+    <t>武器基础_缩放</t>
+  </si>
+  <si>
+    <t>局外待机动作</t>
+  </si>
+  <si>
+    <t>手握武器X偏移</t>
+  </si>
+  <si>
+    <t>手握武器Y偏移</t>
+  </si>
+  <si>
+    <t>男_初始</t>
+  </si>
+  <si>
+    <t>nanzhujue</t>
+  </si>
+  <si>
+    <t>idle</t>
+  </si>
+  <si>
+    <t>女_初始</t>
+  </si>
+  <si>
+    <t>nvzhujue</t>
+  </si>
+  <si>
+    <t>基础史莱姆</t>
+  </si>
+  <si>
+    <t>shilaimu</t>
   </si>
 </sst>
 </file>
@@ -256,7 +313,7 @@
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
-  <fonts count="20">
+  <fonts count="21">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -277,6 +334,12 @@
       <name val="等线"/>
       <charset val="134"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color theme="1"/>
+      <name val="微软雅黑"/>
+      <charset val="134"/>
     </font>
     <font>
       <u/>
@@ -436,6 +499,12 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor theme="9" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
@@ -484,12 +553,6 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor theme="4" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
@@ -609,7 +672,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="10">
+  <borders count="15">
     <border>
       <left/>
       <right/>
@@ -629,6 +692,71 @@
       </top>
       <bottom style="thin">
         <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color theme="0" tint="-0.249977111117893"/>
+      </left>
+      <right style="thin">
+        <color theme="0" tint="-0.249977111117893"/>
+      </right>
+      <top style="thin">
+        <color theme="0" tint="-0.249977111117893"/>
+      </top>
+      <bottom style="thin">
+        <color theme="0" tint="-0.249977111117893"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color theme="0" tint="-0.249946592608417"/>
+      </left>
+      <right style="thin">
+        <color theme="0" tint="-0.249946592608417"/>
+      </right>
+      <top/>
+      <bottom style="thin">
+        <color theme="0" tint="-0.249946592608417"/>
       </bottom>
       <diagonal/>
     </border>
@@ -748,52 +876,52 @@
     <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="2" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="7" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="7" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="8" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="8" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="9" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="8" borderId="10" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="9" borderId="11" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="9" borderId="10" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="10" borderId="12" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="13" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="14" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0">
@@ -802,113 +930,151 @@
     <xf numFmtId="0" fontId="2" fillId="3" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="18" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="19" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="14">
+  <cellXfs count="24">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="22" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="23" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="22" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="23" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="22" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="4" borderId="1" xfId="22" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="2" xfId="22" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="3" xfId="22" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="4" xfId="22" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="23" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="4" borderId="1" xfId="23" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="5" borderId="1" xfId="22" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="2" xfId="23" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="5" borderId="1" xfId="23" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="3" xfId="23" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="4" xfId="23" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="5" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="5" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="6" borderId="1" xfId="22" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="6" borderId="1" xfId="23" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -1230,561 +1396,905 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:AE14"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14"/>
+  <dimension ref="A1:AT15"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25"/>
   <cols>
-    <col min="1" max="1" width="9.25" customWidth="1"/>
-    <col min="2" max="2" width="17.3333333333333" customWidth="1"/>
-    <col min="3" max="3" width="12.4166666666667" style="8" customWidth="1"/>
-    <col min="4" max="6" width="22.5" customWidth="1"/>
-    <col min="7" max="12" width="18.75" customWidth="1"/>
-    <col min="13" max="18" width="18.75" style="9" customWidth="1"/>
-    <col min="19" max="19" width="18.9333333333333" customWidth="1"/>
-    <col min="20" max="20" width="22.9833333333333" customWidth="1"/>
-    <col min="21" max="21" width="15.9583333333333" customWidth="1"/>
-    <col min="22" max="22" width="16.725" customWidth="1"/>
-    <col min="23" max="23" width="17.3" customWidth="1"/>
-    <col min="24" max="24" width="18.55" customWidth="1"/>
-    <col min="25" max="26" width="16.3416666666667" customWidth="1"/>
-    <col min="27" max="28" width="20.2833333333333" customWidth="1"/>
-    <col min="29" max="29" width="19.225" customWidth="1"/>
-    <col min="30" max="30" width="22.875" customWidth="1"/>
-    <col min="31" max="31" width="18.5583333333333" customWidth="1"/>
+    <col min="1" max="1" width="9.25" style="3" customWidth="1"/>
+    <col min="2" max="2" width="17.3333333333333" style="3" customWidth="1"/>
+    <col min="3" max="3" width="12.4166666666667" style="18" customWidth="1"/>
+    <col min="4" max="6" width="22.5" style="3" customWidth="1"/>
+    <col min="7" max="12" width="18.75" style="3" customWidth="1"/>
+    <col min="13" max="18" width="18.75" style="19" customWidth="1"/>
+    <col min="19" max="19" width="18.9333333333333" style="3" customWidth="1"/>
+    <col min="20" max="20" width="22.9833333333333" style="3" customWidth="1"/>
+    <col min="21" max="21" width="15.9583333333333" style="3" customWidth="1"/>
+    <col min="22" max="22" width="16.725" style="3" customWidth="1"/>
+    <col min="23" max="23" width="17.3" style="3" customWidth="1"/>
+    <col min="24" max="24" width="18.55" style="3" customWidth="1"/>
+    <col min="25" max="26" width="16.3416666666667" style="3" customWidth="1"/>
+    <col min="27" max="28" width="20.2833333333333" style="3" customWidth="1"/>
+    <col min="29" max="29" width="19.225" style="3" customWidth="1"/>
+    <col min="30" max="30" width="22.875" style="3" customWidth="1"/>
+    <col min="31" max="31" width="18.5583333333333" style="3" customWidth="1"/>
+    <col min="32" max="32" width="15" style="3" customWidth="1"/>
+    <col min="33" max="33" width="14.875" style="3" customWidth="1"/>
+    <col min="34" max="34" width="15" style="3" customWidth="1"/>
+    <col min="35" max="35" width="14.875" style="3" customWidth="1"/>
+    <col min="36" max="36" width="15" style="3" customWidth="1"/>
+    <col min="37" max="37" width="13.75" style="3" customWidth="1"/>
+    <col min="38" max="38" width="15" style="3" customWidth="1"/>
+    <col min="39" max="39" width="14.875" style="3" customWidth="1"/>
+    <col min="40" max="40" width="15" style="3" customWidth="1"/>
+    <col min="41" max="41" width="14.875" style="3" customWidth="1"/>
+    <col min="42" max="42" width="15" style="3" customWidth="1"/>
+    <col min="43" max="43" width="13.75" style="3" customWidth="1"/>
+    <col min="44" max="44" width="15.75" style="3" customWidth="1"/>
+    <col min="45" max="45" width="14.125" style="3" customWidth="1"/>
+    <col min="46" max="46" width="14" style="3" customWidth="1"/>
+    <col min="47" max="16384" width="9" style="3"/>
   </cols>
   <sheetData>
-    <row r="1" s="1" customFormat="1" spans="1:31">
-      <c r="A1" s="4" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="4" t="s">
+    <row r="1" s="1" customFormat="1" spans="1:46">
+      <c r="A1" s="5" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="5" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="10" t="s">
+      <c r="C1" s="20" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="4" t="s">
+      <c r="D1" s="5" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="4" t="s">
+      <c r="E1" s="5" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="4" t="s">
+      <c r="F1" s="5" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="4" t="s">
+      <c r="G1" s="5" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="4" t="s">
+      <c r="H1" s="5" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="4" t="s">
+      <c r="I1" s="5" t="s">
         <v>8</v>
       </c>
-      <c r="J1" s="4" t="s">
+      <c r="J1" s="5" t="s">
         <v>9</v>
       </c>
-      <c r="K1" s="4" t="s">
+      <c r="K1" s="5" t="s">
         <v>10</v>
       </c>
-      <c r="L1" s="4" t="s">
+      <c r="L1" s="5" t="s">
         <v>11</v>
       </c>
-      <c r="M1" s="4" t="s">
+      <c r="M1" s="5" t="s">
         <v>12</v>
       </c>
-      <c r="N1" s="4" t="s">
+      <c r="N1" s="5" t="s">
         <v>13</v>
       </c>
-      <c r="O1" s="4" t="s">
+      <c r="O1" s="5" t="s">
         <v>14</v>
       </c>
-      <c r="P1" s="4" t="s">
+      <c r="P1" s="5" t="s">
         <v>15</v>
       </c>
-      <c r="Q1" s="4" t="s">
+      <c r="Q1" s="5" t="s">
         <v>16</v>
       </c>
-      <c r="R1" s="4" t="s">
+      <c r="R1" s="5" t="s">
         <v>17</v>
       </c>
-      <c r="S1" s="4" t="s">
+      <c r="S1" s="5" t="s">
         <v>18</v>
       </c>
-      <c r="T1" s="4" t="s">
+      <c r="T1" s="5" t="s">
         <v>19</v>
       </c>
-      <c r="U1" s="4" t="s">
+      <c r="U1" s="5" t="s">
         <v>20</v>
       </c>
-      <c r="V1" s="4" t="s">
+      <c r="V1" s="5" t="s">
         <v>21</v>
       </c>
-      <c r="W1" s="4" t="s">
+      <c r="W1" s="5" t="s">
         <v>22</v>
       </c>
-      <c r="X1" s="4" t="s">
+      <c r="X1" s="5" t="s">
         <v>23</v>
       </c>
-      <c r="Y1" s="4" t="s">
+      <c r="Y1" s="5" t="s">
         <v>24</v>
       </c>
-      <c r="Z1" s="4" t="s">
+      <c r="Z1" s="5" t="s">
         <v>25</v>
       </c>
-      <c r="AA1" s="4" t="s">
+      <c r="AA1" s="5" t="s">
         <v>26</v>
       </c>
-      <c r="AB1" s="4" t="s">
+      <c r="AB1" s="5" t="s">
         <v>27</v>
       </c>
-      <c r="AC1" s="4" t="s">
+      <c r="AC1" s="5" t="s">
         <v>28</v>
       </c>
-      <c r="AD1" s="4" t="s">
+      <c r="AD1" s="5" t="s">
         <v>29</v>
       </c>
-      <c r="AE1" s="4" t="s">
+      <c r="AE1" s="5" t="s">
         <v>30</v>
       </c>
+      <c r="AF1" s="7" t="s">
+        <v>31</v>
+      </c>
+      <c r="AG1" s="8"/>
+      <c r="AH1" s="8"/>
+      <c r="AI1" s="8"/>
+      <c r="AJ1" s="8"/>
+      <c r="AK1" s="9"/>
+      <c r="AL1" s="7" t="s">
+        <v>32</v>
+      </c>
+      <c r="AM1" s="8"/>
+      <c r="AN1" s="8"/>
+      <c r="AO1" s="8"/>
+      <c r="AP1" s="8"/>
+      <c r="AQ1" s="9"/>
+      <c r="AR1" s="5" t="s">
+        <v>33</v>
+      </c>
+      <c r="AS1" s="5" t="s">
+        <v>34</v>
+      </c>
+      <c r="AT1" s="5" t="s">
+        <v>35</v>
+      </c>
     </row>
-    <row r="2" s="2" customFormat="1" spans="1:31">
-      <c r="A2" s="6" t="s">
+    <row r="2" s="2" customFormat="1" spans="1:46">
+      <c r="A2" s="10" t="s">
+        <v>36</v>
+      </c>
+      <c r="B2" s="10" t="s">
+        <v>37</v>
+      </c>
+      <c r="C2" s="21"/>
+      <c r="D2" s="10" t="s">
+        <v>38</v>
+      </c>
+      <c r="E2" s="10" t="s">
+        <v>38</v>
+      </c>
+      <c r="F2" s="10" t="s">
+        <v>38</v>
+      </c>
+      <c r="G2" s="10" t="s">
+        <v>39</v>
+      </c>
+      <c r="H2" s="10" t="s">
+        <v>39</v>
+      </c>
+      <c r="I2" s="10" t="s">
+        <v>39</v>
+      </c>
+      <c r="J2" s="10" t="s">
+        <v>40</v>
+      </c>
+      <c r="K2" s="10" t="s">
+        <v>40</v>
+      </c>
+      <c r="L2" s="10" t="s">
+        <v>39</v>
+      </c>
+      <c r="M2" s="10" t="s">
+        <v>39</v>
+      </c>
+      <c r="N2" s="10" t="s">
+        <v>39</v>
+      </c>
+      <c r="O2" s="10" t="s">
+        <v>39</v>
+      </c>
+      <c r="P2" s="10" t="s">
+        <v>39</v>
+      </c>
+      <c r="Q2" s="10" t="s">
+        <v>39</v>
+      </c>
+      <c r="R2" s="10" t="s">
+        <v>39</v>
+      </c>
+      <c r="S2" s="10" t="s">
+        <v>41</v>
+      </c>
+      <c r="T2" s="10" t="s">
+        <v>41</v>
+      </c>
+      <c r="U2" s="10" t="s">
+        <v>39</v>
+      </c>
+      <c r="V2" s="10" t="s">
+        <v>39</v>
+      </c>
+      <c r="W2" s="10" t="s">
+        <v>39</v>
+      </c>
+      <c r="X2" s="10" t="s">
+        <v>39</v>
+      </c>
+      <c r="Y2" s="10" t="s">
+        <v>39</v>
+      </c>
+      <c r="Z2" s="10" t="s">
+        <v>39</v>
+      </c>
+      <c r="AA2" s="10" t="s">
+        <v>39</v>
+      </c>
+      <c r="AB2" s="10" t="s">
+        <v>39</v>
+      </c>
+      <c r="AC2" s="10" t="s">
+        <v>39</v>
+      </c>
+      <c r="AD2" s="10" t="s">
+        <v>39</v>
+      </c>
+      <c r="AE2" s="10" t="s">
+        <v>37</v>
+      </c>
+      <c r="AF2" s="12" t="s">
         <v>31</v>
       </c>
-      <c r="B2" s="6" t="s">
-        <v>32</v>
-      </c>
-      <c r="C2" s="11"/>
-      <c r="D2" s="6" t="s">
-        <v>33</v>
-      </c>
-      <c r="E2" s="6" t="s">
-        <v>33</v>
-      </c>
-      <c r="F2" s="6" t="s">
-        <v>33</v>
-      </c>
-      <c r="G2" s="6" t="s">
-        <v>34</v>
-      </c>
-      <c r="H2" s="6" t="s">
-        <v>34</v>
-      </c>
-      <c r="I2" s="6" t="s">
-        <v>34</v>
-      </c>
-      <c r="J2" s="6" t="s">
-        <v>35</v>
-      </c>
-      <c r="K2" s="6" t="s">
-        <v>35</v>
-      </c>
-      <c r="L2" s="6" t="s">
-        <v>34</v>
-      </c>
-      <c r="M2" s="6" t="s">
-        <v>34</v>
-      </c>
-      <c r="N2" s="6" t="s">
-        <v>34</v>
-      </c>
-      <c r="O2" s="6" t="s">
-        <v>34</v>
-      </c>
-      <c r="P2" s="6" t="s">
-        <v>34</v>
-      </c>
-      <c r="Q2" s="6" t="s">
-        <v>34</v>
-      </c>
-      <c r="R2" s="6" t="s">
-        <v>34</v>
-      </c>
-      <c r="S2" s="6" t="s">
+      <c r="AG2" s="13"/>
+      <c r="AH2" s="13"/>
+      <c r="AI2" s="13"/>
+      <c r="AJ2" s="13"/>
+      <c r="AK2" s="14"/>
+      <c r="AL2" s="12" t="s">
+        <v>31</v>
+      </c>
+      <c r="AM2" s="13"/>
+      <c r="AN2" s="13"/>
+      <c r="AO2" s="13"/>
+      <c r="AP2" s="13"/>
+      <c r="AQ2" s="14"/>
+      <c r="AR2" s="10" t="s">
+        <v>38</v>
+      </c>
+      <c r="AS2" s="10" t="s">
+        <v>39</v>
+      </c>
+      <c r="AT2" s="10" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="3" s="2" customFormat="1" spans="1:46">
+      <c r="A3" s="10" t="s">
         <v>36</v>
       </c>
-      <c r="T2" s="6" t="s">
-        <v>36</v>
-      </c>
-      <c r="U2" s="6" t="s">
-        <v>34</v>
-      </c>
-      <c r="V2" s="6" t="s">
-        <v>34</v>
-      </c>
-      <c r="W2" s="6" t="s">
-        <v>34</v>
-      </c>
-      <c r="X2" s="6" t="s">
-        <v>34</v>
-      </c>
-      <c r="Y2" s="6" t="s">
-        <v>34</v>
-      </c>
-      <c r="Z2" s="6" t="s">
-        <v>34</v>
-      </c>
-      <c r="AA2" s="6" t="s">
-        <v>34</v>
-      </c>
-      <c r="AB2" s="6" t="s">
-        <v>34</v>
-      </c>
-      <c r="AC2" s="6" t="s">
-        <v>34</v>
-      </c>
-      <c r="AD2" s="6" t="s">
-        <v>34</v>
-      </c>
-      <c r="AE2" s="6" t="s">
-        <v>32</v>
-      </c>
+      <c r="B3" s="10"/>
+      <c r="C3" s="21"/>
+      <c r="D3" s="10"/>
+      <c r="E3" s="10"/>
+      <c r="F3" s="10"/>
+      <c r="G3" s="10"/>
+      <c r="H3" s="10"/>
+      <c r="I3" s="10"/>
+      <c r="J3" s="10"/>
+      <c r="K3" s="10"/>
+      <c r="L3" s="10"/>
+      <c r="M3" s="10"/>
+      <c r="N3" s="10"/>
+      <c r="O3" s="10"/>
+      <c r="P3" s="10"/>
+      <c r="Q3" s="10"/>
+      <c r="R3" s="10"/>
+      <c r="S3" s="10"/>
+      <c r="T3" s="10"/>
+      <c r="U3" s="10"/>
+      <c r="V3" s="10"/>
+      <c r="W3" s="10" t="s">
+        <v>42</v>
+      </c>
+      <c r="X3" s="10" t="s">
+        <v>42</v>
+      </c>
+      <c r="Y3" s="10" t="s">
+        <v>42</v>
+      </c>
+      <c r="Z3" s="10" t="s">
+        <v>42</v>
+      </c>
+      <c r="AA3" s="10" t="s">
+        <v>42</v>
+      </c>
+      <c r="AB3" s="10"/>
+      <c r="AC3" s="10" t="s">
+        <v>42</v>
+      </c>
+      <c r="AD3" s="10" t="s">
+        <v>42</v>
+      </c>
+      <c r="AE3" s="10"/>
+      <c r="AF3" s="10" t="s">
+        <v>39</v>
+      </c>
+      <c r="AG3" s="10" t="s">
+        <v>39</v>
+      </c>
+      <c r="AH3" s="10" t="s">
+        <v>39</v>
+      </c>
+      <c r="AI3" s="10" t="s">
+        <v>39</v>
+      </c>
+      <c r="AJ3" s="10" t="s">
+        <v>39</v>
+      </c>
+      <c r="AK3" s="10" t="s">
+        <v>39</v>
+      </c>
+      <c r="AL3" s="10" t="s">
+        <v>39</v>
+      </c>
+      <c r="AM3" s="10" t="s">
+        <v>39</v>
+      </c>
+      <c r="AN3" s="10" t="s">
+        <v>39</v>
+      </c>
+      <c r="AO3" s="10" t="s">
+        <v>39</v>
+      </c>
+      <c r="AP3" s="10" t="s">
+        <v>39</v>
+      </c>
+      <c r="AQ3" s="10" t="s">
+        <v>39</v>
+      </c>
+      <c r="AR3" s="10"/>
+      <c r="AS3" s="10"/>
+      <c r="AT3" s="10"/>
     </row>
-    <row r="3" s="2" customFormat="1" spans="1:31">
-      <c r="A3" s="6" t="s">
-        <v>37</v>
-      </c>
-      <c r="B3" s="6"/>
-      <c r="C3" s="11"/>
-      <c r="D3" s="6"/>
-      <c r="E3" s="6"/>
-      <c r="F3" s="6"/>
-      <c r="G3" s="6"/>
-      <c r="H3" s="6"/>
-      <c r="I3" s="6"/>
-      <c r="J3" s="6"/>
-      <c r="K3" s="6"/>
-      <c r="L3" s="6"/>
-      <c r="M3" s="6"/>
-      <c r="N3" s="6"/>
-      <c r="O3" s="6"/>
-      <c r="P3" s="6"/>
-      <c r="Q3" s="6"/>
-      <c r="R3" s="6"/>
-      <c r="S3" s="6"/>
-      <c r="T3" s="6"/>
-      <c r="U3" s="6"/>
-      <c r="V3" s="6"/>
-      <c r="W3" s="6" t="s">
-        <v>38</v>
-      </c>
-      <c r="X3" s="6" t="s">
-        <v>38</v>
-      </c>
-      <c r="Y3" s="6" t="s">
-        <v>38</v>
-      </c>
-      <c r="Z3" s="6" t="s">
-        <v>38</v>
-      </c>
-      <c r="AA3" s="6" t="s">
-        <v>38</v>
-      </c>
-      <c r="AB3" s="6"/>
-      <c r="AC3" s="6" t="s">
-        <v>38</v>
-      </c>
-      <c r="AD3" s="6" t="s">
-        <v>38</v>
-      </c>
-      <c r="AE3" s="6"/>
+    <row r="4" s="2" customFormat="1" spans="1:46">
+      <c r="A4" s="10" t="s">
+        <v>43</v>
+      </c>
+      <c r="B4" s="10"/>
+      <c r="C4" s="21"/>
+      <c r="D4" s="10"/>
+      <c r="E4" s="10"/>
+      <c r="F4" s="10"/>
+      <c r="G4" s="10"/>
+      <c r="H4" s="10"/>
+      <c r="I4" s="10"/>
+      <c r="J4" s="10"/>
+      <c r="K4" s="10"/>
+      <c r="L4" s="10"/>
+      <c r="M4" s="10"/>
+      <c r="N4" s="10"/>
+      <c r="O4" s="10"/>
+      <c r="P4" s="10"/>
+      <c r="Q4" s="10"/>
+      <c r="R4" s="10"/>
+      <c r="S4" s="10"/>
+      <c r="T4" s="10"/>
+      <c r="U4" s="10"/>
+      <c r="V4" s="10"/>
+      <c r="W4" s="10"/>
+      <c r="X4" s="10"/>
+      <c r="Y4" s="10"/>
+      <c r="Z4" s="10"/>
+      <c r="AA4" s="10"/>
+      <c r="AB4" s="10"/>
+      <c r="AC4" s="10"/>
+      <c r="AD4" s="10"/>
+      <c r="AE4" s="10"/>
+      <c r="AF4" s="10"/>
+      <c r="AG4" s="10"/>
+      <c r="AH4" s="10"/>
+      <c r="AI4" s="10"/>
+      <c r="AJ4" s="10"/>
+      <c r="AK4" s="10"/>
+      <c r="AL4" s="10"/>
+      <c r="AM4" s="10"/>
+      <c r="AN4" s="10"/>
+      <c r="AO4" s="10"/>
+      <c r="AP4" s="10"/>
+      <c r="AQ4" s="10"/>
+      <c r="AR4" s="10"/>
+      <c r="AS4" s="10"/>
+      <c r="AT4" s="10"/>
     </row>
-    <row r="4" s="1" customFormat="1" spans="1:31">
-      <c r="A4" s="4" t="s">
-        <v>39</v>
-      </c>
-      <c r="B4" s="4" t="s">
-        <v>40</v>
-      </c>
-      <c r="C4" s="10" t="s">
-        <v>41</v>
-      </c>
-      <c r="D4" s="4" t="s">
-        <v>42</v>
-      </c>
-      <c r="E4" s="4" t="s">
-        <v>43</v>
-      </c>
-      <c r="F4" s="4" t="s">
+    <row r="5" s="1" customFormat="1" spans="1:46">
+      <c r="A5" s="5" t="s">
         <v>44</v>
       </c>
-      <c r="G4" s="4" t="s">
+      <c r="B5" s="5" t="s">
         <v>45</v>
       </c>
-      <c r="H4" s="4" t="s">
+      <c r="C5" s="20" t="s">
         <v>46</v>
       </c>
-      <c r="I4" s="4" t="s">
+      <c r="D5" s="5" t="s">
         <v>47</v>
       </c>
-      <c r="J4" s="4" t="s">
+      <c r="E5" s="5" t="s">
         <v>48</v>
       </c>
-      <c r="K4" s="4" t="s">
+      <c r="F5" s="5" t="s">
         <v>49</v>
       </c>
-      <c r="L4" s="4" t="s">
+      <c r="G5" s="5" t="s">
         <v>50</v>
       </c>
-      <c r="M4" s="4" t="s">
+      <c r="H5" s="5" t="s">
         <v>51</v>
       </c>
-      <c r="N4" s="4" t="s">
+      <c r="I5" s="5" t="s">
         <v>52</v>
       </c>
-      <c r="O4" s="4" t="s">
+      <c r="J5" s="5" t="s">
         <v>53</v>
       </c>
-      <c r="P4" s="4" t="s">
+      <c r="K5" s="5" t="s">
         <v>54</v>
       </c>
-      <c r="Q4" s="4" t="s">
+      <c r="L5" s="5" t="s">
         <v>55</v>
       </c>
-      <c r="R4" s="4" t="s">
+      <c r="M5" s="5" t="s">
         <v>56</v>
       </c>
-      <c r="S4" s="4" t="s">
+      <c r="N5" s="5" t="s">
         <v>57</v>
       </c>
-      <c r="T4" s="4" t="s">
+      <c r="O5" s="5" t="s">
         <v>58</v>
       </c>
-      <c r="U4" s="4" t="s">
+      <c r="P5" s="5" t="s">
         <v>59</v>
       </c>
-      <c r="V4" s="4" t="s">
+      <c r="Q5" s="5" t="s">
         <v>60</v>
       </c>
-      <c r="W4" s="4" t="s">
+      <c r="R5" s="5" t="s">
         <v>61</v>
       </c>
-      <c r="X4" s="4" t="s">
+      <c r="S5" s="5" t="s">
         <v>62</v>
       </c>
-      <c r="Y4" s="4" t="s">
+      <c r="T5" s="5" t="s">
         <v>63</v>
       </c>
-      <c r="Z4" s="4" t="s">
+      <c r="U5" s="5" t="s">
         <v>64</v>
       </c>
-      <c r="AA4" s="4" t="s">
+      <c r="V5" s="5" t="s">
         <v>65</v>
       </c>
-      <c r="AB4" s="4" t="s">
+      <c r="W5" s="5" t="s">
         <v>66</v>
       </c>
-      <c r="AC4" s="4" t="s">
+      <c r="X5" s="5" t="s">
         <v>67</v>
       </c>
-      <c r="AD4" s="4" t="s">
+      <c r="Y5" s="5" t="s">
         <v>68</v>
       </c>
-      <c r="AE4" s="4" t="s">
+      <c r="Z5" s="5" t="s">
         <v>69</v>
       </c>
+      <c r="AA5" s="5" t="s">
+        <v>70</v>
+      </c>
+      <c r="AB5" s="5" t="s">
+        <v>71</v>
+      </c>
+      <c r="AC5" s="5" t="s">
+        <v>72</v>
+      </c>
+      <c r="AD5" s="5" t="s">
+        <v>73</v>
+      </c>
+      <c r="AE5" s="5" t="s">
+        <v>74</v>
+      </c>
+      <c r="AF5" s="5" t="s">
+        <v>75</v>
+      </c>
+      <c r="AG5" s="5" t="s">
+        <v>76</v>
+      </c>
+      <c r="AH5" s="5" t="s">
+        <v>77</v>
+      </c>
+      <c r="AI5" s="5" t="s">
+        <v>78</v>
+      </c>
+      <c r="AJ5" s="5" t="s">
+        <v>79</v>
+      </c>
+      <c r="AK5" s="5" t="s">
+        <v>80</v>
+      </c>
+      <c r="AL5" s="5" t="s">
+        <v>75</v>
+      </c>
+      <c r="AM5" s="5" t="s">
+        <v>76</v>
+      </c>
+      <c r="AN5" s="5" t="s">
+        <v>77</v>
+      </c>
+      <c r="AO5" s="5" t="s">
+        <v>78</v>
+      </c>
+      <c r="AP5" s="5" t="s">
+        <v>79</v>
+      </c>
+      <c r="AQ5" s="5" t="s">
+        <v>80</v>
+      </c>
+      <c r="AR5" s="5" t="s">
+        <v>81</v>
+      </c>
+      <c r="AS5" s="5" t="s">
+        <v>82</v>
+      </c>
+      <c r="AT5" s="5" t="s">
+        <v>83</v>
+      </c>
     </row>
-    <row r="5" spans="1:31">
-      <c r="A5" s="12"/>
-      <c r="B5" s="12"/>
-      <c r="C5" s="13"/>
-      <c r="D5" s="12"/>
-      <c r="E5" s="12"/>
-      <c r="F5" s="12"/>
-      <c r="G5" s="12"/>
-      <c r="H5" s="12"/>
-      <c r="I5" s="12"/>
-      <c r="J5" s="12"/>
-      <c r="K5" s="12"/>
-      <c r="L5" s="12"/>
-      <c r="M5" s="12"/>
-      <c r="N5" s="12"/>
-      <c r="O5" s="12"/>
-      <c r="P5" s="12"/>
-      <c r="Q5" s="12"/>
-      <c r="R5" s="12"/>
+    <row r="6" s="17" customFormat="1" ht="16.5" customHeight="1" spans="1:46">
+      <c r="A6" s="19"/>
+      <c r="B6" s="22">
+        <v>11000</v>
+      </c>
+      <c r="C6" s="22" t="s">
+        <v>84</v>
+      </c>
+      <c r="D6" s="15"/>
+      <c r="E6" s="15" t="s">
+        <v>85</v>
+      </c>
+      <c r="F6" s="15"/>
+      <c r="G6" s="15"/>
+      <c r="H6" s="15">
+        <v>0.32</v>
+      </c>
+      <c r="I6" s="15">
+        <v>1</v>
+      </c>
+      <c r="J6" s="15">
+        <v>1</v>
+      </c>
+      <c r="K6" s="15">
+        <v>1</v>
+      </c>
+      <c r="L6" s="15"/>
+      <c r="M6" s="15"/>
+      <c r="N6" s="22">
+        <v>0.32</v>
+      </c>
+      <c r="O6" s="22">
+        <v>0.32</v>
+      </c>
+      <c r="P6" s="15"/>
+      <c r="Q6" s="15"/>
+      <c r="R6" s="15">
+        <v>1</v>
+      </c>
+      <c r="S6" s="15">
+        <v>1</v>
+      </c>
+      <c r="T6" s="15">
+        <v>1</v>
+      </c>
+      <c r="U6" s="22">
+        <v>0.32</v>
+      </c>
+      <c r="V6" s="22">
+        <v>0.64</v>
+      </c>
+      <c r="W6" s="15"/>
+      <c r="X6" s="15"/>
+      <c r="Y6" s="15">
+        <v>255</v>
+      </c>
+      <c r="Z6" s="15">
+        <v>0</v>
+      </c>
+      <c r="AA6" s="15">
+        <v>0</v>
+      </c>
+      <c r="AB6" s="15">
+        <v>0.2</v>
+      </c>
+      <c r="AC6" s="15">
+        <v>0.1</v>
+      </c>
+      <c r="AD6" s="15">
+        <v>0.5</v>
+      </c>
+      <c r="AE6" s="15">
+        <v>0</v>
+      </c>
+      <c r="AF6" s="17">
+        <v>0</v>
+      </c>
+      <c r="AG6" s="17">
+        <v>0</v>
+      </c>
+      <c r="AH6" s="17">
+        <v>0</v>
+      </c>
+      <c r="AI6" s="17">
+        <v>0</v>
+      </c>
+      <c r="AJ6" s="17">
+        <v>0</v>
+      </c>
+      <c r="AK6" s="17">
+        <v>1</v>
+      </c>
+      <c r="AL6" s="17">
+        <v>0</v>
+      </c>
+      <c r="AM6" s="17">
+        <v>0</v>
+      </c>
+      <c r="AN6" s="17">
+        <v>0</v>
+      </c>
+      <c r="AO6" s="17">
+        <v>0</v>
+      </c>
+      <c r="AP6" s="17">
+        <v>0</v>
+      </c>
+      <c r="AQ6" s="17">
+        <v>1</v>
+      </c>
+      <c r="AR6" s="1" t="s">
+        <v>86</v>
+      </c>
     </row>
-    <row r="6" spans="1:31">
-      <c r="A6" s="12"/>
-      <c r="B6" s="12"/>
-      <c r="C6" s="13"/>
-      <c r="D6" s="12"/>
-      <c r="E6" s="12"/>
-      <c r="F6" s="12"/>
-      <c r="G6" s="12"/>
-      <c r="H6" s="12"/>
-      <c r="I6" s="12"/>
-      <c r="J6" s="12"/>
-      <c r="K6" s="12"/>
-      <c r="L6" s="12"/>
-      <c r="M6" s="12"/>
-      <c r="N6" s="12"/>
-      <c r="O6" s="12"/>
-      <c r="P6" s="12"/>
-      <c r="Q6" s="12"/>
-      <c r="R6" s="12"/>
+    <row r="7" ht="16.5" spans="1:46">
+      <c r="A7" s="19"/>
+      <c r="B7" s="22">
+        <v>21000</v>
+      </c>
+      <c r="C7" s="22" t="s">
+        <v>87</v>
+      </c>
+      <c r="D7" s="19"/>
+      <c r="E7" s="19" t="s">
+        <v>88</v>
+      </c>
+      <c r="F7" s="19"/>
+      <c r="G7" s="19"/>
+      <c r="H7" s="15">
+        <v>0.32</v>
+      </c>
+      <c r="I7" s="15">
+        <v>1</v>
+      </c>
+      <c r="J7" s="15">
+        <v>1</v>
+      </c>
+      <c r="K7" s="15">
+        <v>1</v>
+      </c>
+      <c r="L7" s="19"/>
+      <c r="M7" s="19"/>
+      <c r="N7" s="22">
+        <v>0.32</v>
+      </c>
+      <c r="O7" s="22">
+        <v>0.32</v>
+      </c>
+      <c r="P7" s="19"/>
+      <c r="Q7" s="19"/>
+      <c r="R7" s="15">
+        <v>1</v>
+      </c>
+      <c r="S7" s="15">
+        <v>1</v>
+      </c>
+      <c r="T7" s="15">
+        <v>1</v>
+      </c>
+      <c r="U7" s="22">
+        <v>0.32</v>
+      </c>
+      <c r="V7" s="22">
+        <v>0.64</v>
+      </c>
+      <c r="Y7" s="15">
+        <v>255</v>
+      </c>
+      <c r="Z7" s="15">
+        <v>0</v>
+      </c>
+      <c r="AA7" s="15">
+        <v>0</v>
+      </c>
+      <c r="AB7" s="15">
+        <v>0.2</v>
+      </c>
+      <c r="AC7" s="15">
+        <v>0.1</v>
+      </c>
+      <c r="AD7" s="15">
+        <v>0.5</v>
+      </c>
+      <c r="AE7" s="15">
+        <v>0</v>
+      </c>
+      <c r="AF7" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG7" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH7" s="3">
+        <v>0</v>
+      </c>
+      <c r="AI7" s="3">
+        <v>0</v>
+      </c>
+      <c r="AJ7" s="3">
+        <v>0</v>
+      </c>
+      <c r="AK7" s="17">
+        <v>1</v>
+      </c>
+      <c r="AL7" s="3">
+        <v>0</v>
+      </c>
+      <c r="AM7" s="3">
+        <v>0</v>
+      </c>
+      <c r="AN7" s="3">
+        <v>0</v>
+      </c>
+      <c r="AO7" s="3">
+        <v>0</v>
+      </c>
+      <c r="AP7" s="3">
+        <v>0</v>
+      </c>
+      <c r="AQ7" s="17">
+        <v>1</v>
+      </c>
+      <c r="AR7" s="1" t="s">
+        <v>86</v>
+      </c>
     </row>
-    <row r="7" spans="1:31">
-      <c r="A7" s="12"/>
-      <c r="B7" s="12"/>
-      <c r="C7" s="13"/>
-      <c r="D7" s="12"/>
-      <c r="E7" s="12"/>
-      <c r="F7" s="12"/>
-      <c r="G7" s="12"/>
-      <c r="H7" s="12"/>
-      <c r="I7" s="12"/>
-      <c r="J7" s="12"/>
-      <c r="K7" s="12"/>
-      <c r="L7" s="12"/>
-      <c r="M7" s="12"/>
-      <c r="N7" s="12"/>
-      <c r="O7" s="12"/>
-      <c r="P7" s="12"/>
-      <c r="Q7" s="12"/>
-      <c r="R7" s="12"/>
+    <row r="8" spans="1:46">
+      <c r="A8" s="19"/>
+      <c r="B8" s="19"/>
+      <c r="C8" s="23"/>
+      <c r="D8" s="19"/>
+      <c r="E8" s="19"/>
+      <c r="F8" s="19"/>
+      <c r="G8" s="19"/>
+      <c r="H8" s="19"/>
+      <c r="I8" s="19"/>
+      <c r="J8" s="19"/>
+      <c r="K8" s="19"/>
+      <c r="L8" s="19"/>
     </row>
-    <row r="8" spans="1:31">
-      <c r="A8" s="12"/>
-      <c r="B8" s="12"/>
-      <c r="C8" s="13"/>
-      <c r="D8" s="12"/>
-      <c r="E8" s="12"/>
-      <c r="F8" s="12"/>
-      <c r="G8" s="12"/>
-      <c r="H8" s="12"/>
-      <c r="I8" s="12"/>
-      <c r="J8" s="12"/>
-      <c r="K8" s="12"/>
-      <c r="L8" s="12"/>
-      <c r="M8" s="12"/>
-      <c r="N8" s="12"/>
-      <c r="O8" s="12"/>
-      <c r="P8" s="12"/>
-      <c r="Q8" s="12"/>
-      <c r="R8" s="12"/>
+    <row r="9" spans="1:46">
+      <c r="A9" s="19"/>
+      <c r="B9" s="19"/>
+      <c r="C9" s="23"/>
+      <c r="D9" s="19"/>
+      <c r="E9" s="19"/>
+      <c r="F9" s="19"/>
+      <c r="G9" s="19"/>
+      <c r="H9" s="19"/>
+      <c r="I9" s="19"/>
+      <c r="J9" s="19"/>
+      <c r="K9" s="19"/>
+      <c r="L9" s="19"/>
     </row>
-    <row r="9" spans="1:31">
-      <c r="A9" s="12"/>
-      <c r="B9" s="12"/>
-      <c r="C9" s="13"/>
-      <c r="D9" s="12"/>
-      <c r="E9" s="12"/>
-      <c r="F9" s="12"/>
-      <c r="G9" s="12"/>
-      <c r="H9" s="12"/>
-      <c r="I9" s="12"/>
-      <c r="J9" s="12"/>
-      <c r="K9" s="12"/>
-      <c r="L9" s="12"/>
-      <c r="M9" s="12"/>
-      <c r="N9" s="12"/>
-      <c r="O9" s="12"/>
-      <c r="P9" s="12"/>
-      <c r="Q9" s="12"/>
-      <c r="R9" s="12"/>
+    <row r="10" spans="1:46">
+      <c r="A10" s="19"/>
+      <c r="B10" s="19"/>
+      <c r="C10" s="23"/>
+      <c r="D10" s="19"/>
+      <c r="E10" s="19"/>
+      <c r="F10" s="19"/>
+      <c r="G10" s="19"/>
+      <c r="H10" s="19"/>
+      <c r="I10" s="19"/>
+      <c r="J10" s="19"/>
+      <c r="K10" s="19"/>
+      <c r="L10" s="19"/>
     </row>
-    <row r="10" spans="1:31">
-      <c r="A10" s="12"/>
-      <c r="B10" s="12"/>
-      <c r="C10" s="13"/>
-      <c r="D10" s="12"/>
-      <c r="E10" s="12"/>
-      <c r="F10" s="12"/>
-      <c r="G10" s="12"/>
-      <c r="H10" s="12"/>
-      <c r="I10" s="12"/>
-      <c r="J10" s="12"/>
-      <c r="K10" s="12"/>
-      <c r="L10" s="12"/>
-      <c r="M10" s="12"/>
-      <c r="N10" s="12"/>
-      <c r="O10" s="12"/>
-      <c r="P10" s="12"/>
-      <c r="Q10" s="12"/>
-      <c r="R10" s="12"/>
+    <row r="11" spans="1:46">
+      <c r="A11" s="19"/>
+      <c r="B11" s="19"/>
+      <c r="C11" s="23"/>
+      <c r="D11" s="19"/>
+      <c r="E11" s="19"/>
+      <c r="F11" s="19"/>
+      <c r="G11" s="19"/>
+      <c r="H11" s="19"/>
+      <c r="I11" s="19"/>
+      <c r="J11" s="19"/>
+      <c r="K11" s="19"/>
+      <c r="L11" s="19"/>
     </row>
-    <row r="11" spans="1:31">
-      <c r="A11" s="12"/>
-      <c r="B11" s="12"/>
-      <c r="C11" s="13"/>
-      <c r="D11" s="12"/>
-      <c r="E11" s="12"/>
-      <c r="F11" s="12"/>
-      <c r="G11" s="12"/>
-      <c r="H11" s="12"/>
-      <c r="I11" s="12"/>
-      <c r="J11" s="12"/>
-      <c r="K11" s="12"/>
-      <c r="L11" s="12"/>
-      <c r="M11" s="12"/>
-      <c r="N11" s="12"/>
-      <c r="O11" s="12"/>
-      <c r="P11" s="12"/>
-      <c r="Q11" s="12"/>
-      <c r="R11" s="12"/>
+    <row r="12" spans="1:46">
+      <c r="A12" s="19"/>
+      <c r="B12" s="19"/>
+      <c r="C12" s="23"/>
+      <c r="D12" s="19"/>
+      <c r="E12" s="19"/>
+      <c r="F12" s="19"/>
+      <c r="G12" s="19"/>
+      <c r="H12" s="19"/>
+      <c r="I12" s="19"/>
+      <c r="J12" s="19"/>
+      <c r="K12" s="19"/>
+      <c r="L12" s="19"/>
     </row>
-    <row r="12" spans="1:31">
-      <c r="A12" s="12"/>
-      <c r="B12" s="12"/>
-      <c r="C12" s="13"/>
-      <c r="D12" s="12"/>
-      <c r="E12" s="12"/>
-      <c r="F12" s="12"/>
-      <c r="G12" s="12"/>
-      <c r="H12" s="12"/>
-      <c r="I12" s="12"/>
-      <c r="J12" s="12"/>
-      <c r="K12" s="12"/>
-      <c r="L12" s="12"/>
-      <c r="M12" s="12"/>
-      <c r="N12" s="12"/>
-      <c r="O12" s="12"/>
-      <c r="P12" s="12"/>
-      <c r="Q12" s="12"/>
-      <c r="R12" s="12"/>
+    <row r="13" spans="1:46">
+      <c r="A13" s="19"/>
+      <c r="B13" s="19"/>
+      <c r="C13" s="23"/>
+      <c r="D13" s="19"/>
+      <c r="E13" s="19"/>
+      <c r="F13" s="19"/>
+      <c r="G13" s="19"/>
+      <c r="H13" s="19"/>
+      <c r="I13" s="19"/>
+      <c r="J13" s="19"/>
+      <c r="K13" s="19"/>
+      <c r="L13" s="19"/>
     </row>
-    <row r="13" spans="1:31">
-      <c r="A13" s="12"/>
-      <c r="B13" s="12"/>
-      <c r="C13" s="13"/>
-      <c r="D13" s="12"/>
-      <c r="E13" s="12"/>
-      <c r="F13" s="12"/>
-      <c r="G13" s="12"/>
-      <c r="H13" s="12"/>
-      <c r="I13" s="12"/>
-      <c r="J13" s="12"/>
-      <c r="K13" s="12"/>
-      <c r="L13" s="12"/>
-      <c r="M13" s="12"/>
-      <c r="N13" s="12"/>
-      <c r="O13" s="12"/>
-      <c r="P13" s="12"/>
-      <c r="Q13" s="12"/>
-      <c r="R13" s="12"/>
+    <row r="14" spans="1:46">
+      <c r="A14" s="19"/>
+      <c r="B14" s="19"/>
+      <c r="C14" s="23"/>
+      <c r="D14" s="19"/>
+      <c r="E14" s="19"/>
+      <c r="F14" s="19"/>
+      <c r="G14" s="19"/>
+      <c r="H14" s="19"/>
+      <c r="I14" s="19"/>
+      <c r="J14" s="19"/>
+      <c r="K14" s="19"/>
+      <c r="L14" s="19"/>
     </row>
-    <row r="14" spans="1:31">
-      <c r="A14" s="12"/>
-      <c r="B14" s="12"/>
-      <c r="C14" s="13"/>
-      <c r="D14" s="12"/>
-      <c r="E14" s="12"/>
-      <c r="F14" s="12"/>
-      <c r="G14" s="12"/>
-      <c r="H14" s="12"/>
-      <c r="I14" s="12"/>
-      <c r="J14" s="12"/>
-      <c r="K14" s="12"/>
-      <c r="L14" s="12"/>
-      <c r="M14" s="12"/>
-      <c r="N14" s="12"/>
-      <c r="O14" s="12"/>
-      <c r="P14" s="12"/>
-      <c r="Q14" s="12"/>
-      <c r="R14" s="12"/>
+    <row r="15" spans="1:46">
+      <c r="A15" s="19"/>
+      <c r="B15" s="19"/>
+      <c r="C15" s="23"/>
+      <c r="D15" s="19"/>
+      <c r="E15" s="19"/>
+      <c r="F15" s="19"/>
+      <c r="G15" s="19"/>
+      <c r="H15" s="19"/>
+      <c r="I15" s="19"/>
+      <c r="J15" s="19"/>
+      <c r="K15" s="19"/>
+      <c r="L15" s="19"/>
     </row>
   </sheetData>
+  <mergeCells count="4">
+    <mergeCell ref="AF1:AK1"/>
+    <mergeCell ref="AL1:AQ1"/>
+    <mergeCell ref="AF2:AK2"/>
+    <mergeCell ref="AL2:AQ2"/>
+  </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait"/>
   <headerFooter/>
@@ -1794,374 +2304,670 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:AE4"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14" outlineLevelRow="3"/>
+  <dimension ref="A1:BA5"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25" outlineLevelRow="4"/>
   <cols>
-    <col min="2" max="2" width="12.625" customWidth="1"/>
-    <col min="3" max="3" width="15.375" style="3" customWidth="1"/>
-    <col min="4" max="4" width="26.625" customWidth="1"/>
-    <col min="5" max="5" width="23.5" customWidth="1"/>
-    <col min="6" max="6" width="18" customWidth="1"/>
-    <col min="7" max="7" width="19.625" customWidth="1"/>
-    <col min="8" max="8" width="19.5" customWidth="1"/>
-    <col min="9" max="9" width="21.625" customWidth="1"/>
-    <col min="10" max="10" width="14.125" customWidth="1"/>
-    <col min="11" max="11" width="18.75" customWidth="1"/>
-    <col min="12" max="12" width="23.875" customWidth="1"/>
-    <col min="13" max="13" width="20.875" customWidth="1"/>
-    <col min="14" max="14" width="19.75" customWidth="1"/>
-    <col min="15" max="15" width="17.25" customWidth="1"/>
-    <col min="16" max="16" width="24.375" customWidth="1"/>
-    <col min="17" max="17" width="23.5" customWidth="1"/>
-    <col min="18" max="18" width="27.375" customWidth="1"/>
-    <col min="19" max="19" width="25.125" customWidth="1"/>
-    <col min="20" max="20" width="24.875" customWidth="1"/>
-    <col min="21" max="21" width="19.25" customWidth="1"/>
-    <col min="22" max="22" width="23.875" customWidth="1"/>
-    <col min="23" max="23" width="20.75" customWidth="1"/>
-    <col min="24" max="24" width="20.125" customWidth="1"/>
-    <col min="25" max="25" width="22.625" customWidth="1"/>
-    <col min="26" max="26" width="20.125" customWidth="1"/>
-    <col min="27" max="27" width="24.75" customWidth="1"/>
-    <col min="28" max="28" width="27" customWidth="1"/>
-    <col min="29" max="29" width="25.875" customWidth="1"/>
-    <col min="30" max="30" width="28.25" customWidth="1"/>
-    <col min="31" max="31" width="22.75" customWidth="1"/>
+    <col min="1" max="1" width="9" style="3"/>
+    <col min="2" max="2" width="12.625" style="3" customWidth="1"/>
+    <col min="3" max="3" width="15.375" style="4" customWidth="1"/>
+    <col min="4" max="4" width="26.625" style="3" customWidth="1"/>
+    <col min="5" max="5" width="23.5" style="3" customWidth="1"/>
+    <col min="6" max="6" width="18" style="3" customWidth="1"/>
+    <col min="7" max="7" width="19.625" style="3" customWidth="1"/>
+    <col min="8" max="8" width="19.5" style="3" customWidth="1"/>
+    <col min="9" max="9" width="21.625" style="3" customWidth="1"/>
+    <col min="10" max="10" width="14.125" style="3" customWidth="1"/>
+    <col min="11" max="11" width="18.75" style="3" customWidth="1"/>
+    <col min="12" max="12" width="23.875" style="3" customWidth="1"/>
+    <col min="13" max="13" width="20.875" style="3" customWidth="1"/>
+    <col min="14" max="14" width="19.75" style="3" customWidth="1"/>
+    <col min="15" max="15" width="17.25" style="3" customWidth="1"/>
+    <col min="16" max="16" width="24.375" style="3" customWidth="1"/>
+    <col min="17" max="17" width="23.5" style="3" customWidth="1"/>
+    <col min="18" max="18" width="27.375" style="3" customWidth="1"/>
+    <col min="19" max="19" width="25.125" style="3" customWidth="1"/>
+    <col min="20" max="20" width="24.875" style="3" customWidth="1"/>
+    <col min="21" max="21" width="19.25" style="3" customWidth="1"/>
+    <col min="22" max="22" width="23.875" style="3" customWidth="1"/>
+    <col min="23" max="23" width="20.75" style="3" customWidth="1"/>
+    <col min="24" max="24" width="20.125" style="3" customWidth="1"/>
+    <col min="25" max="25" width="22.625" style="3" customWidth="1"/>
+    <col min="26" max="26" width="20.125" style="3" customWidth="1"/>
+    <col min="27" max="27" width="24.75" style="3" customWidth="1"/>
+    <col min="28" max="28" width="27" style="3" customWidth="1"/>
+    <col min="29" max="29" width="25.875" style="3" customWidth="1"/>
+    <col min="30" max="30" width="28.25" style="3" customWidth="1"/>
+    <col min="31" max="31" width="22.75" style="3" customWidth="1"/>
+    <col min="32" max="33" width="24" style="3" customWidth="1"/>
+    <col min="34" max="34" width="15" style="3" customWidth="1"/>
+    <col min="35" max="35" width="14.875" style="3" customWidth="1"/>
+    <col min="36" max="36" width="15" style="3" customWidth="1"/>
+    <col min="37" max="37" width="13.75" style="3" customWidth="1"/>
+    <col min="38" max="38" width="15" style="3" customWidth="1"/>
+    <col min="39" max="39" width="14.875" style="3" customWidth="1"/>
+    <col min="40" max="40" width="15" style="3" customWidth="1"/>
+    <col min="41" max="41" width="14.875" style="3" customWidth="1"/>
+    <col min="42" max="42" width="15" style="3" customWidth="1"/>
+    <col min="43" max="43" width="13.75" style="3" customWidth="1"/>
+    <col min="44" max="44" width="15.75" style="3" customWidth="1"/>
+    <col min="45" max="45" width="14.75" style="3" customWidth="1"/>
+    <col min="46" max="46" width="14.625" style="3" customWidth="1"/>
+    <col min="47" max="16384" width="9" style="3"/>
   </cols>
   <sheetData>
-    <row r="1" s="1" customFormat="1" spans="1:31">
-      <c r="A1" s="4" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="4" t="s">
+    <row r="1" s="1" customFormat="1" spans="1:53">
+      <c r="A1" s="5" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="5" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="5" t="s">
+      <c r="C1" s="6" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="4" t="s">
+      <c r="D1" s="5" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="4" t="s">
+      <c r="E1" s="5" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="4" t="s">
+      <c r="F1" s="5" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="4" t="s">
+      <c r="G1" s="5" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="4" t="s">
+      <c r="H1" s="5" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="4" t="s">
+      <c r="I1" s="5" t="s">
         <v>8</v>
       </c>
-      <c r="J1" s="4" t="s">
+      <c r="J1" s="5" t="s">
         <v>9</v>
       </c>
-      <c r="K1" s="4" t="s">
+      <c r="K1" s="5" t="s">
         <v>10</v>
       </c>
-      <c r="L1" s="4" t="s">
+      <c r="L1" s="5" t="s">
         <v>11</v>
       </c>
-      <c r="M1" s="4" t="s">
+      <c r="M1" s="5" t="s">
         <v>12</v>
       </c>
-      <c r="N1" s="4" t="s">
+      <c r="N1" s="5" t="s">
         <v>13</v>
       </c>
-      <c r="O1" s="4" t="s">
+      <c r="O1" s="5" t="s">
         <v>14</v>
       </c>
-      <c r="P1" s="4" t="s">
+      <c r="P1" s="5" t="s">
         <v>15</v>
       </c>
-      <c r="Q1" s="4" t="s">
+      <c r="Q1" s="5" t="s">
         <v>16</v>
       </c>
-      <c r="R1" s="4" t="s">
+      <c r="R1" s="5" t="s">
         <v>17</v>
       </c>
-      <c r="S1" s="4" t="s">
+      <c r="S1" s="5" t="s">
         <v>18</v>
       </c>
-      <c r="T1" s="4" t="s">
+      <c r="T1" s="5" t="s">
         <v>19</v>
       </c>
-      <c r="U1" s="4" t="s">
+      <c r="U1" s="5" t="s">
+        <v>20</v>
+      </c>
+      <c r="V1" s="5" t="s">
+        <v>21</v>
+      </c>
+      <c r="W1" s="5" t="s">
+        <v>22</v>
+      </c>
+      <c r="X1" s="5" t="s">
+        <v>23</v>
+      </c>
+      <c r="Y1" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="Z1" s="5" t="s">
+        <v>25</v>
+      </c>
+      <c r="AA1" s="5" t="s">
+        <v>26</v>
+      </c>
+      <c r="AB1" s="5" t="s">
+        <v>27</v>
+      </c>
+      <c r="AC1" s="5" t="s">
+        <v>28</v>
+      </c>
+      <c r="AD1" s="5" t="s">
+        <v>29</v>
+      </c>
+      <c r="AE1" s="5" t="s">
+        <v>30</v>
+      </c>
+      <c r="AF1" s="7" t="s">
+        <v>31</v>
+      </c>
+      <c r="AG1" s="8"/>
+      <c r="AH1" s="8"/>
+      <c r="AI1" s="8"/>
+      <c r="AJ1" s="8"/>
+      <c r="AK1" s="9"/>
+      <c r="AL1" s="7" t="s">
+        <v>32</v>
+      </c>
+      <c r="AM1" s="8"/>
+      <c r="AN1" s="8"/>
+      <c r="AO1" s="8"/>
+      <c r="AP1" s="8"/>
+      <c r="AQ1" s="9"/>
+      <c r="AR1" s="5" t="s">
+        <v>33</v>
+      </c>
+      <c r="AS1" s="5" t="s">
+        <v>34</v>
+      </c>
+      <c r="AT1" s="5" t="s">
+        <v>35</v>
+      </c>
+      <c r="AU1" s="5"/>
+      <c r="AV1" s="5"/>
+      <c r="AW1" s="5"/>
+      <c r="AX1" s="5"/>
+      <c r="AY1" s="5"/>
+      <c r="AZ1" s="5"/>
+      <c r="BA1" s="5"/>
+    </row>
+    <row r="2" s="2" customFormat="1" spans="1:53">
+      <c r="A2" s="10" t="s">
+        <v>36</v>
+      </c>
+      <c r="B2" s="10" t="s">
+        <v>37</v>
+      </c>
+      <c r="C2" s="11"/>
+      <c r="D2" s="10" t="s">
+        <v>38</v>
+      </c>
+      <c r="E2" s="10" t="s">
+        <v>38</v>
+      </c>
+      <c r="F2" s="10" t="s">
+        <v>38</v>
+      </c>
+      <c r="G2" s="10" t="s">
+        <v>39</v>
+      </c>
+      <c r="H2" s="10" t="s">
+        <v>39</v>
+      </c>
+      <c r="I2" s="10" t="s">
+        <v>39</v>
+      </c>
+      <c r="J2" s="10" t="s">
+        <v>40</v>
+      </c>
+      <c r="K2" s="10" t="s">
+        <v>40</v>
+      </c>
+      <c r="L2" s="10" t="s">
+        <v>39</v>
+      </c>
+      <c r="M2" s="10" t="s">
+        <v>39</v>
+      </c>
+      <c r="N2" s="10" t="s">
+        <v>39</v>
+      </c>
+      <c r="O2" s="10" t="s">
+        <v>39</v>
+      </c>
+      <c r="P2" s="10" t="s">
+        <v>39</v>
+      </c>
+      <c r="Q2" s="10" t="s">
+        <v>39</v>
+      </c>
+      <c r="R2" s="10" t="s">
+        <v>39</v>
+      </c>
+      <c r="S2" s="10" t="s">
+        <v>41</v>
+      </c>
+      <c r="T2" s="10" t="s">
+        <v>41</v>
+      </c>
+      <c r="U2" s="10" t="s">
+        <v>39</v>
+      </c>
+      <c r="V2" s="10" t="s">
+        <v>39</v>
+      </c>
+      <c r="W2" s="10" t="s">
+        <v>39</v>
+      </c>
+      <c r="X2" s="10" t="s">
+        <v>39</v>
+      </c>
+      <c r="Y2" s="10" t="s">
+        <v>39</v>
+      </c>
+      <c r="Z2" s="10" t="s">
+        <v>39</v>
+      </c>
+      <c r="AA2" s="10" t="s">
+        <v>39</v>
+      </c>
+      <c r="AB2" s="10" t="s">
+        <v>39</v>
+      </c>
+      <c r="AC2" s="10" t="s">
+        <v>39</v>
+      </c>
+      <c r="AD2" s="10" t="s">
+        <v>39</v>
+      </c>
+      <c r="AE2" s="10" t="s">
+        <v>37</v>
+      </c>
+      <c r="AF2" s="12" t="s">
+        <v>31</v>
+      </c>
+      <c r="AG2" s="13"/>
+      <c r="AH2" s="13"/>
+      <c r="AI2" s="13"/>
+      <c r="AJ2" s="13"/>
+      <c r="AK2" s="14"/>
+      <c r="AL2" s="12" t="s">
+        <v>31</v>
+      </c>
+      <c r="AM2" s="13"/>
+      <c r="AN2" s="13"/>
+      <c r="AO2" s="13"/>
+      <c r="AP2" s="13"/>
+      <c r="AQ2" s="14"/>
+      <c r="AR2" s="10" t="s">
+        <v>38</v>
+      </c>
+      <c r="AS2" s="10" t="s">
+        <v>39</v>
+      </c>
+      <c r="AT2" s="10" t="s">
+        <v>39</v>
+      </c>
+      <c r="AU2" s="10"/>
+      <c r="AV2" s="10"/>
+      <c r="AW2" s="10"/>
+      <c r="AX2" s="10"/>
+      <c r="AY2" s="10"/>
+      <c r="AZ2" s="10"/>
+      <c r="BA2" s="10"/>
+    </row>
+    <row r="3" s="2" customFormat="1" spans="1:53">
+      <c r="A3" s="10" t="s">
+        <v>43</v>
+      </c>
+      <c r="B3" s="10"/>
+      <c r="C3" s="11"/>
+      <c r="D3" s="10"/>
+      <c r="E3" s="10"/>
+      <c r="F3" s="10"/>
+      <c r="G3" s="10"/>
+      <c r="H3" s="10"/>
+      <c r="I3" s="10"/>
+      <c r="J3" s="10"/>
+      <c r="K3" s="10"/>
+      <c r="L3" s="10"/>
+      <c r="M3" s="10"/>
+      <c r="N3" s="10"/>
+      <c r="O3" s="10"/>
+      <c r="P3" s="10"/>
+      <c r="Q3" s="10"/>
+      <c r="R3" s="10"/>
+      <c r="S3" s="10"/>
+      <c r="T3" s="10"/>
+      <c r="U3" s="10"/>
+      <c r="V3" s="10"/>
+      <c r="W3" s="10" t="s">
+        <v>42</v>
+      </c>
+      <c r="X3" s="10" t="s">
+        <v>42</v>
+      </c>
+      <c r="Y3" s="10" t="s">
+        <v>42</v>
+      </c>
+      <c r="Z3" s="10" t="s">
+        <v>42</v>
+      </c>
+      <c r="AA3" s="10" t="s">
+        <v>42</v>
+      </c>
+      <c r="AB3" s="10"/>
+      <c r="AC3" s="10" t="s">
+        <v>42</v>
+      </c>
+      <c r="AD3" s="10" t="s">
+        <v>42</v>
+      </c>
+      <c r="AE3" s="10"/>
+      <c r="AF3" s="10" t="s">
+        <v>39</v>
+      </c>
+      <c r="AG3" s="10" t="s">
+        <v>39</v>
+      </c>
+      <c r="AH3" s="10" t="s">
+        <v>39</v>
+      </c>
+      <c r="AI3" s="10" t="s">
+        <v>39</v>
+      </c>
+      <c r="AJ3" s="10" t="s">
+        <v>39</v>
+      </c>
+      <c r="AK3" s="10" t="s">
+        <v>39</v>
+      </c>
+      <c r="AL3" s="10" t="s">
+        <v>39</v>
+      </c>
+      <c r="AM3" s="10" t="s">
+        <v>39</v>
+      </c>
+      <c r="AN3" s="10" t="s">
+        <v>39</v>
+      </c>
+      <c r="AO3" s="10" t="s">
+        <v>39</v>
+      </c>
+      <c r="AP3" s="10" t="s">
+        <v>39</v>
+      </c>
+      <c r="AQ3" s="10" t="s">
+        <v>39</v>
+      </c>
+      <c r="AR3" s="10"/>
+      <c r="AS3" s="10"/>
+      <c r="AT3" s="10"/>
+      <c r="AU3" s="10"/>
+      <c r="AV3" s="10"/>
+      <c r="AW3" s="10"/>
+      <c r="AX3" s="10"/>
+      <c r="AY3" s="10"/>
+      <c r="AZ3" s="10"/>
+      <c r="BA3" s="10"/>
+    </row>
+    <row r="4" s="1" customFormat="1" spans="1:53">
+      <c r="A4" s="5" t="s">
+        <v>44</v>
+      </c>
+      <c r="B4" s="5" t="s">
+        <v>45</v>
+      </c>
+      <c r="C4" s="6" t="s">
+        <v>46</v>
+      </c>
+      <c r="D4" s="5" t="s">
+        <v>47</v>
+      </c>
+      <c r="E4" s="5" t="s">
+        <v>48</v>
+      </c>
+      <c r="F4" s="5" t="s">
+        <v>49</v>
+      </c>
+      <c r="G4" s="5" t="s">
+        <v>50</v>
+      </c>
+      <c r="H4" s="5" t="s">
+        <v>51</v>
+      </c>
+      <c r="I4" s="5" t="s">
+        <v>52</v>
+      </c>
+      <c r="J4" s="5" t="s">
+        <v>53</v>
+      </c>
+      <c r="K4" s="5" t="s">
+        <v>54</v>
+      </c>
+      <c r="L4" s="5" t="s">
+        <v>55</v>
+      </c>
+      <c r="M4" s="5" t="s">
+        <v>56</v>
+      </c>
+      <c r="N4" s="5" t="s">
+        <v>57</v>
+      </c>
+      <c r="O4" s="5" t="s">
+        <v>58</v>
+      </c>
+      <c r="P4" s="5" t="s">
+        <v>59</v>
+      </c>
+      <c r="Q4" s="5" t="s">
+        <v>60</v>
+      </c>
+      <c r="R4" s="5" t="s">
+        <v>61</v>
+      </c>
+      <c r="S4" s="5" t="s">
+        <v>62</v>
+      </c>
+      <c r="T4" s="5" t="s">
+        <v>63</v>
+      </c>
+      <c r="U4" s="5" t="s">
+        <v>64</v>
+      </c>
+      <c r="V4" s="5" t="s">
+        <v>65</v>
+      </c>
+      <c r="W4" s="5" t="s">
+        <v>66</v>
+      </c>
+      <c r="X4" s="5" t="s">
+        <v>67</v>
+      </c>
+      <c r="Y4" s="5" t="s">
+        <v>68</v>
+      </c>
+      <c r="Z4" s="5" t="s">
+        <v>69</v>
+      </c>
+      <c r="AA4" s="5" t="s">
         <v>70</v>
       </c>
-      <c r="V1" s="4" t="s">
+      <c r="AB4" s="5" t="s">
         <v>71</v>
       </c>
-      <c r="W1" s="4" t="s">
-        <v>22</v>
-      </c>
-      <c r="X1" s="4" t="s">
-        <v>23</v>
-      </c>
-      <c r="Y1" s="4" t="s">
-        <v>24</v>
-      </c>
-      <c r="Z1" s="4" t="s">
-        <v>25</v>
-      </c>
-      <c r="AA1" s="4" t="s">
-        <v>26</v>
-      </c>
-      <c r="AB1" s="4" t="s">
-        <v>27</v>
-      </c>
-      <c r="AC1" s="4" t="s">
-        <v>28</v>
-      </c>
-      <c r="AD1" s="4" t="s">
-        <v>29</v>
-      </c>
-      <c r="AE1" s="4" t="s">
-        <v>30</v>
-      </c>
+      <c r="AC4" s="5" t="s">
+        <v>72</v>
+      </c>
+      <c r="AD4" s="5" t="s">
+        <v>73</v>
+      </c>
+      <c r="AE4" s="5" t="s">
+        <v>74</v>
+      </c>
+      <c r="AF4" s="5" t="s">
+        <v>75</v>
+      </c>
+      <c r="AG4" s="5" t="s">
+        <v>76</v>
+      </c>
+      <c r="AH4" s="5" t="s">
+        <v>77</v>
+      </c>
+      <c r="AI4" s="5" t="s">
+        <v>78</v>
+      </c>
+      <c r="AJ4" s="5" t="s">
+        <v>79</v>
+      </c>
+      <c r="AK4" s="5" t="s">
+        <v>80</v>
+      </c>
+      <c r="AL4" s="5" t="s">
+        <v>75</v>
+      </c>
+      <c r="AM4" s="5" t="s">
+        <v>76</v>
+      </c>
+      <c r="AN4" s="5" t="s">
+        <v>77</v>
+      </c>
+      <c r="AO4" s="5" t="s">
+        <v>78</v>
+      </c>
+      <c r="AP4" s="5" t="s">
+        <v>79</v>
+      </c>
+      <c r="AQ4" s="5" t="s">
+        <v>80</v>
+      </c>
+      <c r="AR4" s="5" t="s">
+        <v>81</v>
+      </c>
+      <c r="AS4" s="5" t="s">
+        <v>82</v>
+      </c>
+      <c r="AT4" s="5" t="s">
+        <v>83</v>
+      </c>
+      <c r="AU4" s="5"/>
+      <c r="AV4" s="5"/>
+      <c r="AW4" s="5"/>
+      <c r="AX4" s="5"/>
+      <c r="AY4" s="5"/>
+      <c r="AZ4" s="5"/>
+      <c r="BA4" s="5"/>
     </row>
-    <row r="2" s="2" customFormat="1" spans="1:31">
-      <c r="A2" s="6" t="s">
-        <v>31</v>
-      </c>
-      <c r="B2" s="6" t="s">
-        <v>32</v>
-      </c>
-      <c r="C2" s="7"/>
-      <c r="D2" s="6" t="s">
-        <v>33</v>
-      </c>
-      <c r="E2" s="6" t="s">
-        <v>33</v>
-      </c>
-      <c r="F2" s="6" t="s">
-        <v>33</v>
-      </c>
-      <c r="G2" s="6" t="s">
-        <v>34</v>
-      </c>
-      <c r="H2" s="6" t="s">
-        <v>34</v>
-      </c>
-      <c r="I2" s="6" t="s">
-        <v>34</v>
-      </c>
-      <c r="J2" s="6" t="s">
-        <v>35</v>
-      </c>
-      <c r="K2" s="6" t="s">
-        <v>35</v>
-      </c>
-      <c r="L2" s="6" t="s">
-        <v>34</v>
-      </c>
-      <c r="M2" s="6" t="s">
-        <v>34</v>
-      </c>
-      <c r="N2" s="6" t="s">
-        <v>34</v>
-      </c>
-      <c r="O2" s="6" t="s">
-        <v>34</v>
-      </c>
-      <c r="P2" s="6" t="s">
-        <v>34</v>
-      </c>
-      <c r="Q2" s="6" t="s">
-        <v>34</v>
-      </c>
-      <c r="R2" s="6" t="s">
-        <v>34</v>
-      </c>
-      <c r="S2" s="6" t="s">
-        <v>36</v>
-      </c>
-      <c r="T2" s="6" t="s">
-        <v>36</v>
-      </c>
-      <c r="U2" s="6" t="s">
-        <v>34</v>
-      </c>
-      <c r="V2" s="6" t="s">
-        <v>34</v>
-      </c>
-      <c r="W2" s="6" t="s">
-        <v>34</v>
-      </c>
-      <c r="X2" s="6" t="s">
-        <v>34</v>
-      </c>
-      <c r="Y2" s="6" t="s">
-        <v>34</v>
-      </c>
-      <c r="Z2" s="6" t="s">
-        <v>34</v>
-      </c>
-      <c r="AA2" s="6" t="s">
-        <v>34</v>
-      </c>
-      <c r="AB2" s="6" t="s">
-        <v>34</v>
-      </c>
-      <c r="AC2" s="6" t="s">
-        <v>34</v>
-      </c>
-      <c r="AD2" s="6" t="s">
-        <v>34</v>
-      </c>
-      <c r="AE2" s="6" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="3" s="2" customFormat="1" spans="1:31">
-      <c r="A3" s="6" t="s">
-        <v>37</v>
-      </c>
-      <c r="B3" s="6"/>
-      <c r="C3" s="7"/>
-      <c r="D3" s="6"/>
-      <c r="E3" s="6"/>
-      <c r="F3" s="6"/>
-      <c r="G3" s="6"/>
-      <c r="H3" s="6"/>
-      <c r="I3" s="6"/>
-      <c r="J3" s="6"/>
-      <c r="K3" s="6"/>
-      <c r="L3" s="6"/>
-      <c r="M3" s="6"/>
-      <c r="N3" s="6"/>
-      <c r="O3" s="6"/>
-      <c r="P3" s="6"/>
-      <c r="Q3" s="6"/>
-      <c r="R3" s="6"/>
-      <c r="S3" s="6"/>
-      <c r="T3" s="6"/>
-      <c r="U3" s="6"/>
-      <c r="V3" s="6"/>
-      <c r="W3" s="6" t="s">
-        <v>38</v>
-      </c>
-      <c r="X3" s="6" t="s">
-        <v>38</v>
-      </c>
-      <c r="Y3" s="6" t="s">
-        <v>38</v>
-      </c>
-      <c r="Z3" s="6" t="s">
-        <v>38</v>
-      </c>
-      <c r="AA3" s="6" t="s">
-        <v>38</v>
-      </c>
-      <c r="AB3" s="6"/>
-      <c r="AC3" s="6" t="s">
-        <v>38</v>
-      </c>
-      <c r="AD3" s="6" t="s">
-        <v>38</v>
-      </c>
-      <c r="AE3" s="6"/>
-    </row>
-    <row r="4" s="1" customFormat="1" spans="1:31">
-      <c r="A4" s="4" t="s">
-        <v>39</v>
-      </c>
-      <c r="B4" s="4" t="s">
-        <v>40</v>
-      </c>
-      <c r="C4" s="5" t="s">
-        <v>41</v>
-      </c>
-      <c r="D4" s="4" t="s">
-        <v>42</v>
-      </c>
-      <c r="E4" s="4" t="s">
-        <v>43</v>
-      </c>
-      <c r="F4" s="4" t="s">
-        <v>44</v>
-      </c>
-      <c r="G4" s="4" t="s">
-        <v>45</v>
-      </c>
-      <c r="H4" s="4" t="s">
-        <v>46</v>
-      </c>
-      <c r="I4" s="4" t="s">
-        <v>47</v>
-      </c>
-      <c r="J4" s="4" t="s">
-        <v>48</v>
-      </c>
-      <c r="K4" s="4" t="s">
-        <v>49</v>
-      </c>
-      <c r="L4" s="4" t="s">
-        <v>50</v>
-      </c>
-      <c r="M4" s="4" t="s">
-        <v>51</v>
-      </c>
-      <c r="N4" s="4" t="s">
-        <v>52</v>
-      </c>
-      <c r="O4" s="4" t="s">
-        <v>53</v>
-      </c>
-      <c r="P4" s="4" t="s">
-        <v>54</v>
-      </c>
-      <c r="Q4" s="4" t="s">
-        <v>55</v>
-      </c>
-      <c r="R4" s="4" t="s">
-        <v>56</v>
-      </c>
-      <c r="S4" s="4" t="s">
-        <v>57</v>
-      </c>
-      <c r="T4" s="4" t="s">
-        <v>58</v>
-      </c>
-      <c r="U4" s="4" t="s">
-        <v>59</v>
-      </c>
-      <c r="V4" s="4" t="s">
-        <v>60</v>
-      </c>
-      <c r="W4" s="4" t="s">
-        <v>61</v>
-      </c>
-      <c r="X4" s="4" t="s">
-        <v>62</v>
-      </c>
-      <c r="Y4" s="4" t="s">
-        <v>63</v>
-      </c>
-      <c r="Z4" s="4" t="s">
-        <v>64</v>
-      </c>
-      <c r="AA4" s="4" t="s">
-        <v>65</v>
-      </c>
-      <c r="AB4" s="4" t="s">
-        <v>66</v>
-      </c>
-      <c r="AC4" s="4" t="s">
-        <v>67</v>
-      </c>
-      <c r="AD4" s="4" t="s">
-        <v>68</v>
-      </c>
-      <c r="AE4" s="4" t="s">
-        <v>69</v>
+    <row r="5" ht="16.5" spans="1:53">
+      <c r="B5" s="15">
+        <v>100111</v>
+      </c>
+      <c r="C5" s="16" t="s">
+        <v>89</v>
+      </c>
+      <c r="D5" s="15"/>
+      <c r="E5" s="15" t="s">
+        <v>90</v>
+      </c>
+      <c r="F5" s="15"/>
+      <c r="G5" s="15"/>
+      <c r="H5" s="15">
+        <v>1.5</v>
+      </c>
+      <c r="I5" s="15">
+        <v>1</v>
+      </c>
+      <c r="J5" s="15"/>
+      <c r="K5" s="15">
+        <v>1</v>
+      </c>
+      <c r="L5" s="15"/>
+      <c r="M5" s="15">
+        <v>0.07</v>
+      </c>
+      <c r="N5" s="15">
+        <v>0.4</v>
+      </c>
+      <c r="O5" s="15">
+        <v>0.4</v>
+      </c>
+      <c r="P5" s="15"/>
+      <c r="Q5" s="15"/>
+      <c r="R5" s="15">
+        <v>1</v>
+      </c>
+      <c r="S5" s="15">
+        <v>1</v>
+      </c>
+      <c r="T5" s="15">
+        <v>1</v>
+      </c>
+      <c r="U5" s="15">
+        <v>0.3</v>
+      </c>
+      <c r="V5" s="15">
+        <v>0.8</v>
+      </c>
+      <c r="W5" s="15"/>
+      <c r="X5" s="15">
+        <v>0.5</v>
+      </c>
+      <c r="Y5" s="15">
+        <v>255</v>
+      </c>
+      <c r="Z5" s="15">
+        <v>0</v>
+      </c>
+      <c r="AA5" s="15">
+        <v>0</v>
+      </c>
+      <c r="AB5" s="15">
+        <v>0.2</v>
+      </c>
+      <c r="AC5" s="15">
+        <v>0.1</v>
+      </c>
+      <c r="AD5" s="15">
+        <v>0.5</v>
+      </c>
+      <c r="AE5" s="15">
+        <v>0</v>
+      </c>
+      <c r="AF5" s="17">
+        <v>0</v>
+      </c>
+      <c r="AG5" s="17">
+        <v>0</v>
+      </c>
+      <c r="AH5" s="17">
+        <v>0</v>
+      </c>
+      <c r="AI5" s="17">
+        <v>0</v>
+      </c>
+      <c r="AJ5" s="17">
+        <v>0</v>
+      </c>
+      <c r="AK5" s="17">
+        <v>0</v>
+      </c>
+      <c r="AL5" s="17">
+        <v>0</v>
+      </c>
+      <c r="AM5" s="17">
+        <v>0</v>
+      </c>
+      <c r="AN5" s="17">
+        <v>0</v>
+      </c>
+      <c r="AO5" s="17">
+        <v>0</v>
+      </c>
+      <c r="AP5" s="17">
+        <v>0</v>
+      </c>
+      <c r="AQ5" s="17">
+        <v>0</v>
       </c>
     </row>
   </sheetData>
+  <mergeCells count="4">
+    <mergeCell ref="AF1:AK1"/>
+    <mergeCell ref="AL1:AQ1"/>
+    <mergeCell ref="AF2:AK2"/>
+    <mergeCell ref="AL2:AQ2"/>
+  </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <headerFooter/>
 </worksheet>
